--- a/docs/Airmius_Use_Cases_Testmatrix_testfreundlich org.xlsx
+++ b/docs/Airmius_Use_Cases_Testmatrix_testfreundlich org.xlsx
@@ -17,7 +17,6 @@
     <sheet name="Tabelle2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -7225,7 +7224,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -8086,7 +8085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R666"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" customWidth="1"/>
@@ -8104,10 +8103,10 @@
     <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="A1" s="22"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18">
       <c r="A2" s="22"/>
       <c r="B2" s="7" t="s">
         <v>1971</v>
@@ -8117,27 +8116,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18">
       <c r="A3" s="22"/>
       <c r="B3" s="7" t="s">
         <v>1972</v>
       </c>
       <c r="C3" s="18">
         <f>COUNTIF(B5:B800,"&gt;0")</f>
-        <v>313</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="22"/>
       <c r="B4" s="7" t="s">
         <v>1973</v>
       </c>
       <c r="C4" s="18">
         <f>COUNTIF(B5:B800,"=0")</f>
-        <v>331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="20" t="s">
         <v>0</v>
       </c>
@@ -8193,7 +8192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
       <c r="A6" s="22" t="s">
         <v>82</v>
       </c>
@@ -8249,7 +8248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
       <c r="A7" s="22" t="s">
         <v>240</v>
       </c>
@@ -8305,7 +8304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
       <c r="A8" s="22" t="s">
         <v>263</v>
       </c>
@@ -8361,7 +8360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
       <c r="A9" s="22" t="s">
         <v>342</v>
       </c>
@@ -8417,7 +8416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
       <c r="A10" s="22" t="s">
         <v>99</v>
       </c>
@@ -8473,7 +8472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
       <c r="A11" s="22" t="s">
         <v>101</v>
       </c>
@@ -8529,7 +8528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="195" hidden="1">
       <c r="A12" s="22" t="s">
         <v>103</v>
       </c>
@@ -8585,7 +8584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="75" hidden="1">
       <c r="A13" s="22" t="s">
         <v>122</v>
       </c>
@@ -8641,7 +8640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="75" hidden="1">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -8697,7 +8696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="75" hidden="1">
       <c r="A15" s="22" t="s">
         <v>134</v>
       </c>
@@ -8753,7 +8752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="75" hidden="1">
       <c r="A16" s="22" t="s">
         <v>150</v>
       </c>
@@ -8809,7 +8808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="60" hidden="1">
       <c r="A17" s="22" t="s">
         <v>220</v>
       </c>
@@ -8865,7 +8864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="75">
       <c r="A18" s="22" t="s">
         <v>225</v>
       </c>
@@ -8921,7 +8920,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="75" hidden="1">
       <c r="A19" s="22" t="s">
         <v>1970</v>
       </c>
@@ -8977,7 +8976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="60" hidden="1">
       <c r="A20" s="22" t="s">
         <v>414</v>
       </c>
@@ -9033,7 +9032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="60">
       <c r="A21" s="22" t="s">
         <v>417</v>
       </c>
@@ -9089,7 +9088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="60" hidden="1">
       <c r="A22" s="22" t="s">
         <v>420</v>
       </c>
@@ -9145,7 +9144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="90" hidden="1">
       <c r="A23" s="22" t="s">
         <v>430</v>
       </c>
@@ -9201,7 +9200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="90" hidden="1">
       <c r="A24" s="22" t="s">
         <v>439</v>
       </c>
@@ -9257,7 +9256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="90" hidden="1">
       <c r="A25" s="22" t="s">
         <v>442</v>
       </c>
@@ -9313,7 +9312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="90">
       <c r="A26" s="22" t="s">
         <v>445</v>
       </c>
@@ -9369,7 +9368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="90">
       <c r="A27" s="22" t="s">
         <v>448</v>
       </c>
@@ -9425,7 +9424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="60" hidden="1">
       <c r="A28" s="22" t="s">
         <v>457</v>
       </c>
@@ -9481,7 +9480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="60" hidden="1">
       <c r="A29" s="22" t="s">
         <v>460</v>
       </c>
@@ -9537,7 +9536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="60" hidden="1">
       <c r="A30" s="22" t="s">
         <v>463</v>
       </c>
@@ -9593,7 +9592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="60" hidden="1">
       <c r="A31" s="22" t="s">
         <v>466</v>
       </c>
@@ -9649,7 +9648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="60">
       <c r="A32" s="22" t="s">
         <v>494</v>
       </c>
@@ -9705,7 +9704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="75" hidden="1">
       <c r="A33" s="22" t="s">
         <v>500</v>
       </c>
@@ -9761,7 +9760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="75" hidden="1">
       <c r="A34" s="22" t="s">
         <v>503</v>
       </c>
@@ -9817,7 +9816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="60">
       <c r="A35" s="22" t="s">
         <v>514</v>
       </c>
@@ -9873,7 +9872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="60" hidden="1">
       <c r="A36" s="22" t="s">
         <v>563</v>
       </c>
@@ -9929,7 +9928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="60" hidden="1">
       <c r="A37" s="22" t="s">
         <v>565</v>
       </c>
@@ -9985,7 +9984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="60">
       <c r="A38" s="22" t="s">
         <v>574</v>
       </c>
@@ -10041,7 +10040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="75">
       <c r="A39" s="22" t="s">
         <v>577</v>
       </c>
@@ -10097,7 +10096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="75">
       <c r="A40" s="22" t="s">
         <v>580</v>
       </c>
@@ -10153,7 +10152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="75">
       <c r="A41" s="22" t="s">
         <v>583</v>
       </c>
@@ -10209,7 +10208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="75">
       <c r="A42" s="22" t="s">
         <v>586</v>
       </c>
@@ -10265,7 +10264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="60">
       <c r="A43" s="22" t="s">
         <v>589</v>
       </c>
@@ -10321,7 +10320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="60" hidden="1">
       <c r="A44" s="22" t="s">
         <v>591</v>
       </c>
@@ -10377,7 +10376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="60" hidden="1">
       <c r="A45" s="22" t="s">
         <v>595</v>
       </c>
@@ -10433,7 +10432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="60" hidden="1">
       <c r="A46" s="22" t="s">
         <v>598</v>
       </c>
@@ -10489,7 +10488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="60" hidden="1">
       <c r="A47" s="22" t="s">
         <v>601</v>
       </c>
@@ -10545,7 +10544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="26" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" s="26" customFormat="1" ht="60" hidden="1">
       <c r="A48" s="22" t="s">
         <v>604</v>
       </c>
@@ -10601,7 +10600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="60" hidden="1">
       <c r="A49" s="22" t="s">
         <v>606</v>
       </c>
@@ -10657,7 +10656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="60" hidden="1">
       <c r="A50" s="22" t="s">
         <v>608</v>
       </c>
@@ -10713,7 +10712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="60" hidden="1">
       <c r="A51" s="22" t="s">
         <v>612</v>
       </c>
@@ -10769,7 +10768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="60" hidden="1">
       <c r="A52" s="22" t="s">
         <v>614</v>
       </c>
@@ -10825,7 +10824,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="60" hidden="1">
       <c r="A53" s="22" t="s">
         <v>616</v>
       </c>
@@ -10881,7 +10880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="60" hidden="1">
       <c r="A54" s="22" t="s">
         <v>618</v>
       </c>
@@ -10937,7 +10936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="345">
       <c r="A55" s="22" t="s">
         <v>684</v>
       </c>
@@ -10993,7 +10992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="135" hidden="1">
       <c r="A56" s="22" t="s">
         <v>687</v>
       </c>
@@ -11049,7 +11048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="135" hidden="1">
       <c r="A57" s="22" t="s">
         <v>689</v>
       </c>
@@ -11105,7 +11104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="135">
       <c r="A58" s="22" t="s">
         <v>692</v>
       </c>
@@ -11161,7 +11160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="135">
       <c r="A59" s="22" t="s">
         <v>700</v>
       </c>
@@ -11217,7 +11216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="135">
       <c r="A60" s="22" t="s">
         <v>703</v>
       </c>
@@ -11273,7 +11272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="135">
       <c r="A61" s="22" t="s">
         <v>704</v>
       </c>
@@ -11329,7 +11328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="60">
       <c r="A62" s="22" t="s">
         <v>706</v>
       </c>
@@ -11385,7 +11384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="75">
       <c r="A63" s="22" t="s">
         <v>711</v>
       </c>
@@ -11441,7 +11440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="75">
       <c r="A64" s="22" t="s">
         <v>714</v>
       </c>
@@ -11497,7 +11496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="60" hidden="1">
       <c r="A65" s="22" t="s">
         <v>717</v>
       </c>
@@ -11553,7 +11552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="60">
       <c r="A66" s="22" t="s">
         <v>720</v>
       </c>
@@ -11609,7 +11608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="60" hidden="1">
       <c r="A67" s="22" t="s">
         <v>723</v>
       </c>
@@ -11665,7 +11664,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="60" hidden="1">
       <c r="A68" s="22" t="s">
         <v>726</v>
       </c>
@@ -11721,7 +11720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="75" hidden="1">
       <c r="A69" s="22" t="s">
         <v>729</v>
       </c>
@@ -11777,7 +11776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="150" hidden="1">
       <c r="A70" s="22" t="s">
         <v>745</v>
       </c>
@@ -11833,7 +11832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="150" hidden="1">
       <c r="A71" s="22" t="s">
         <v>749</v>
       </c>
@@ -11889,7 +11888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="150" hidden="1">
       <c r="A72" s="22" t="s">
         <v>752</v>
       </c>
@@ -11945,7 +11944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="150" hidden="1">
       <c r="A73" s="22" t="s">
         <v>755</v>
       </c>
@@ -12001,7 +12000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="150" hidden="1">
       <c r="A74" s="22" t="s">
         <v>758</v>
       </c>
@@ -12057,7 +12056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="150" hidden="1">
       <c r="A75" s="22" t="s">
         <v>761</v>
       </c>
@@ -12113,7 +12112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="150" hidden="1">
       <c r="A76" s="22" t="s">
         <v>764</v>
       </c>
@@ -12169,7 +12168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="150" hidden="1">
       <c r="A77" s="22" t="s">
         <v>766</v>
       </c>
@@ -12225,7 +12224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="150" hidden="1">
       <c r="A78" s="22" t="s">
         <v>769</v>
       </c>
@@ -12281,7 +12280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="150" hidden="1">
       <c r="A79" s="22" t="s">
         <v>772</v>
       </c>
@@ -12337,7 +12336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="150">
       <c r="A80" s="22" t="s">
         <v>775</v>
       </c>
@@ -12393,7 +12392,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="60" hidden="1">
       <c r="A81" s="22" t="s">
         <v>778</v>
       </c>
@@ -12449,7 +12448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="60" hidden="1">
       <c r="A82" s="22" t="s">
         <v>786</v>
       </c>
@@ -12505,7 +12504,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="60" hidden="1">
       <c r="A83" s="22" t="s">
         <v>788</v>
       </c>
@@ -12561,7 +12560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="60" hidden="1">
       <c r="A84" s="22" t="s">
         <v>789</v>
       </c>
@@ -12617,7 +12616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="60" hidden="1">
       <c r="A85" s="22" t="s">
         <v>791</v>
       </c>
@@ -12673,7 +12672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="60">
       <c r="A86" s="22" t="s">
         <v>792</v>
       </c>
@@ -12729,7 +12728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="60" hidden="1">
       <c r="A87" s="22" t="s">
         <v>795</v>
       </c>
@@ -12785,7 +12784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="60" hidden="1">
       <c r="A88" s="22" t="s">
         <v>798</v>
       </c>
@@ -12841,7 +12840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="60" hidden="1">
       <c r="A89" s="22" t="s">
         <v>799</v>
       </c>
@@ -12897,7 +12896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="60" hidden="1">
       <c r="A90" s="22" t="s">
         <v>800</v>
       </c>
@@ -12953,7 +12952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="60" hidden="1">
       <c r="A91" s="22" t="s">
         <v>802</v>
       </c>
@@ -13009,7 +13008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="60" hidden="1">
       <c r="A92" s="22" t="s">
         <v>805</v>
       </c>
@@ -13065,7 +13064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="135" hidden="1">
       <c r="A93" s="22" t="s">
         <v>808</v>
       </c>
@@ -13121,7 +13120,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="135" hidden="1">
       <c r="A94" s="22" t="s">
         <v>810</v>
       </c>
@@ -13177,7 +13176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="135" hidden="1">
       <c r="A95" s="22" t="s">
         <v>812</v>
       </c>
@@ -13233,7 +13232,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="135" hidden="1">
       <c r="A96" s="22" t="s">
         <v>814</v>
       </c>
@@ -13289,12 +13288,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="135">
       <c r="A97" s="22" t="s">
         <v>816</v>
       </c>
       <c r="B97" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" s="18" t="s">
         <v>817</v>
@@ -13345,7 +13344,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="135" hidden="1">
       <c r="A98" s="22" t="s">
         <v>819</v>
       </c>
@@ -13401,7 +13400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="135" hidden="1">
       <c r="A99" s="22" t="s">
         <v>821</v>
       </c>
@@ -13457,7 +13456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="409.5" hidden="1">
       <c r="A100" s="22" t="s">
         <v>832</v>
       </c>
@@ -13513,12 +13512,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="409.5">
       <c r="A101" s="22" t="s">
         <v>835</v>
       </c>
       <c r="B101" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" s="18" t="s">
         <v>836</v>
@@ -13569,7 +13568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="409.5" hidden="1">
       <c r="A102" s="22" t="s">
         <v>852</v>
       </c>
@@ -13625,7 +13624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="409.5" hidden="1">
       <c r="A103" s="22" t="s">
         <v>854</v>
       </c>
@@ -13681,7 +13680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="409.5" hidden="1">
       <c r="A104" s="22" t="s">
         <v>856</v>
       </c>
@@ -13737,7 +13736,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="409.5" hidden="1">
       <c r="A105" s="22" t="s">
         <v>858</v>
       </c>
@@ -13793,7 +13792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="409.5" hidden="1">
       <c r="A106" s="22" t="s">
         <v>860</v>
       </c>
@@ -13849,7 +13848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="409.5" hidden="1">
       <c r="A107" s="22" t="s">
         <v>866</v>
       </c>
@@ -13905,12 +13904,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="409.5">
       <c r="A108" s="22" t="s">
         <v>868</v>
       </c>
       <c r="B108" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>869</v>
@@ -13961,7 +13960,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="409.5">
       <c r="A109" s="22" t="s">
         <v>871</v>
       </c>
@@ -14017,7 +14016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="409.5">
       <c r="A110" s="22" t="s">
         <v>873</v>
       </c>
@@ -14073,7 +14072,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="409.5">
       <c r="A111" s="22" t="s">
         <v>879</v>
       </c>
@@ -14129,7 +14128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="409.5">
       <c r="A112" s="22" t="s">
         <v>881</v>
       </c>
@@ -14185,7 +14184,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="60" hidden="1">
       <c r="A113" s="22" t="s">
         <v>884</v>
       </c>
@@ -14241,7 +14240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="60" hidden="1">
       <c r="A114" s="22" t="s">
         <v>890</v>
       </c>
@@ -14297,7 +14296,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="60" hidden="1">
       <c r="A115" s="22" t="s">
         <v>893</v>
       </c>
@@ -14353,7 +14352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="60" hidden="1">
       <c r="A116" s="22" t="s">
         <v>894</v>
       </c>
@@ -14409,7 +14408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="60" hidden="1">
       <c r="A117" s="22" t="s">
         <v>896</v>
       </c>
@@ -14465,7 +14464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="60" hidden="1">
       <c r="A118" s="22" t="s">
         <v>901</v>
       </c>
@@ -14521,7 +14520,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="75" hidden="1">
       <c r="A119" s="22" t="s">
         <v>909</v>
       </c>
@@ -14577,7 +14576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="60" hidden="1">
       <c r="A120" s="22" t="s">
         <v>912</v>
       </c>
@@ -14633,7 +14632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="75" hidden="1">
       <c r="A121" s="22" t="s">
         <v>915</v>
       </c>
@@ -14689,7 +14688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="75" hidden="1">
       <c r="A122" s="22" t="s">
         <v>918</v>
       </c>
@@ -14745,7 +14744,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="60">
       <c r="A123" s="22" t="s">
         <v>921</v>
       </c>
@@ -14801,7 +14800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="60">
       <c r="A124" s="22" t="s">
         <v>924</v>
       </c>
@@ -14857,7 +14856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="60">
       <c r="A125" s="22" t="s">
         <v>927</v>
       </c>
@@ -14913,7 +14912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="60" hidden="1">
       <c r="A126" s="22" t="s">
         <v>930</v>
       </c>
@@ -14969,7 +14968,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="75">
       <c r="A127" s="22" t="s">
         <v>933</v>
       </c>
@@ -15025,7 +15024,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="75">
       <c r="A128" s="22" t="s">
         <v>936</v>
       </c>
@@ -15081,7 +15080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="75">
       <c r="A129" s="22" t="s">
         <v>939</v>
       </c>
@@ -15137,7 +15136,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="75">
       <c r="A130" s="22" t="s">
         <v>942</v>
       </c>
@@ -15193,7 +15192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="60" hidden="1">
       <c r="A131" s="22" t="s">
         <v>945</v>
       </c>
@@ -15249,7 +15248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="60">
       <c r="A132" s="22" t="s">
         <v>948</v>
       </c>
@@ -15305,7 +15304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="60">
       <c r="A133" s="22" t="s">
         <v>950</v>
       </c>
@@ -15361,7 +15360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="60" hidden="1">
       <c r="A134" s="22" t="s">
         <v>953</v>
       </c>
@@ -15417,7 +15416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="60" hidden="1">
       <c r="A135" s="22" t="s">
         <v>955</v>
       </c>
@@ -15473,7 +15472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="60" hidden="1">
       <c r="A136" s="22" t="s">
         <v>957</v>
       </c>
@@ -15529,7 +15528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="60" hidden="1">
       <c r="A137" s="22" t="s">
         <v>959</v>
       </c>
@@ -15585,7 +15584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="60" hidden="1">
       <c r="A138" s="22" t="s">
         <v>962</v>
       </c>
@@ -15641,7 +15640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="60" hidden="1">
       <c r="A139" s="22" t="s">
         <v>964</v>
       </c>
@@ -15697,7 +15696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="60" hidden="1">
       <c r="A140" s="22" t="s">
         <v>967</v>
       </c>
@@ -15753,7 +15752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="60" hidden="1">
       <c r="A141" s="22" t="s">
         <v>972</v>
       </c>
@@ -15809,7 +15808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="60">
       <c r="A142" s="22" t="s">
         <v>978</v>
       </c>
@@ -15865,7 +15864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="60">
       <c r="A143" s="22" t="s">
         <v>981</v>
       </c>
@@ -15921,7 +15920,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="60">
       <c r="A144" s="22" t="s">
         <v>984</v>
       </c>
@@ -15977,7 +15976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="60">
       <c r="A145" s="22" t="s">
         <v>987</v>
       </c>
@@ -16033,7 +16032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="60" hidden="1">
       <c r="A146" s="22" t="s">
         <v>990</v>
       </c>
@@ -16089,7 +16088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="60">
       <c r="A147" s="22" t="s">
         <v>993</v>
       </c>
@@ -16145,7 +16144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="60">
       <c r="A148" s="22" t="s">
         <v>996</v>
       </c>
@@ -16201,7 +16200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="60">
       <c r="A149" s="22" t="s">
         <v>999</v>
       </c>
@@ -16257,7 +16256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="60">
       <c r="A150" s="22" t="s">
         <v>1002</v>
       </c>
@@ -16313,7 +16312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="60">
       <c r="A151" s="22" t="s">
         <v>1005</v>
       </c>
@@ -16369,7 +16368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="60">
       <c r="A152" s="22" t="s">
         <v>1010</v>
       </c>
@@ -16425,7 +16424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="75">
       <c r="A153" s="22" t="s">
         <v>1012</v>
       </c>
@@ -16481,7 +16480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="60">
       <c r="A154" s="22" t="s">
         <v>1015</v>
       </c>
@@ -16537,7 +16536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="60">
       <c r="A155" s="22" t="s">
         <v>1018</v>
       </c>
@@ -16593,7 +16592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="60">
       <c r="A156" s="22" t="s">
         <v>1021</v>
       </c>
@@ -16649,7 +16648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="60">
       <c r="A157" s="22" t="s">
         <v>1024</v>
       </c>
@@ -16705,7 +16704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="60">
       <c r="A158" s="22" t="s">
         <v>1027</v>
       </c>
@@ -16761,7 +16760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="60">
       <c r="A159" s="22" t="s">
         <v>1030</v>
       </c>
@@ -16817,7 +16816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="60">
       <c r="A160" s="22" t="s">
         <v>1033</v>
       </c>
@@ -16873,7 +16872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="60">
       <c r="A161" s="22" t="s">
         <v>1036</v>
       </c>
@@ -16929,7 +16928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="60">
       <c r="A162" s="22" t="s">
         <v>1038</v>
       </c>
@@ -16985,7 +16984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="60">
       <c r="A163" s="22" t="s">
         <v>1040</v>
       </c>
@@ -17041,7 +17040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="60">
       <c r="A164" s="22" t="s">
         <v>1044</v>
       </c>
@@ -17097,7 +17096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="60">
       <c r="A165" s="22" t="s">
         <v>1047</v>
       </c>
@@ -17153,7 +17152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="60">
       <c r="A166" s="22" t="s">
         <v>1050</v>
       </c>
@@ -17209,7 +17208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="60">
       <c r="A167" s="22" t="s">
         <v>1053</v>
       </c>
@@ -17265,7 +17264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="60">
       <c r="A168" s="22" t="s">
         <v>1056</v>
       </c>
@@ -17321,7 +17320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="60">
       <c r="A169" s="22" t="s">
         <v>1059</v>
       </c>
@@ -17377,7 +17376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="75">
       <c r="A170" s="22" t="s">
         <v>1062</v>
       </c>
@@ -17433,7 +17432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="60">
       <c r="A171" s="22" t="s">
         <v>1065</v>
       </c>
@@ -17489,7 +17488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="60">
       <c r="A172" s="22" t="s">
         <v>1068</v>
       </c>
@@ -17545,7 +17544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="60">
       <c r="A173" s="22" t="s">
         <v>1071</v>
       </c>
@@ -17601,7 +17600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="60">
       <c r="A174" s="22" t="s">
         <v>1074</v>
       </c>
@@ -17657,7 +17656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="60">
       <c r="A175" s="22" t="s">
         <v>1076</v>
       </c>
@@ -17713,7 +17712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="60">
       <c r="A176" s="22" t="s">
         <v>1078</v>
       </c>
@@ -17769,7 +17768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="60">
       <c r="A177" s="22" t="s">
         <v>1080</v>
       </c>
@@ -17825,7 +17824,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="60">
       <c r="A178" s="22" t="s">
         <v>1082</v>
       </c>
@@ -17881,7 +17880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="60">
       <c r="A179" s="22" t="s">
         <v>1084</v>
       </c>
@@ -17937,7 +17936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="60">
       <c r="A180" s="22" t="s">
         <v>1087</v>
       </c>
@@ -17993,7 +17992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="60">
       <c r="A181" s="22" t="s">
         <v>1090</v>
       </c>
@@ -18049,7 +18048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="60">
       <c r="A182" s="22" t="s">
         <v>1093</v>
       </c>
@@ -18105,7 +18104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="60">
       <c r="A183" s="22" t="s">
         <v>1095</v>
       </c>
@@ -18161,7 +18160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="60">
       <c r="A184" s="22" t="s">
         <v>1098</v>
       </c>
@@ -18217,7 +18216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="60">
       <c r="A185" s="22" t="s">
         <v>1100</v>
       </c>
@@ -18273,7 +18272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="60">
       <c r="A186" s="22" t="s">
         <v>1103</v>
       </c>
@@ -18329,7 +18328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="75">
       <c r="A187" s="22" t="s">
         <v>1106</v>
       </c>
@@ -18385,7 +18384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="60">
       <c r="A188" s="22" t="s">
         <v>1109</v>
       </c>
@@ -18441,7 +18440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="60">
       <c r="A189" s="22" t="s">
         <v>1111</v>
       </c>
@@ -18497,7 +18496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="60">
       <c r="A190" s="22" t="s">
         <v>1113</v>
       </c>
@@ -18553,7 +18552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="60">
       <c r="A191" s="22" t="s">
         <v>1116</v>
       </c>
@@ -18609,7 +18608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="60">
       <c r="A192" s="22" t="s">
         <v>1119</v>
       </c>
@@ -18665,7 +18664,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="60">
       <c r="A193" s="22" t="s">
         <v>1122</v>
       </c>
@@ -18721,7 +18720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="60">
       <c r="A194" s="22" t="s">
         <v>1125</v>
       </c>
@@ -18777,7 +18776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="60">
       <c r="A195" s="22" t="s">
         <v>1127</v>
       </c>
@@ -18833,7 +18832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="90">
       <c r="A196" s="22" t="s">
         <v>1130</v>
       </c>
@@ -18889,7 +18888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="90">
       <c r="A197" s="22" t="s">
         <v>1133</v>
       </c>
@@ -18945,7 +18944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="75">
       <c r="A198" s="22" t="s">
         <v>1136</v>
       </c>
@@ -19001,7 +19000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="75">
       <c r="A199" s="22" t="s">
         <v>1140</v>
       </c>
@@ -19057,7 +19056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="75">
       <c r="A200" s="22" t="s">
         <v>1143</v>
       </c>
@@ -19113,7 +19112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="75">
       <c r="A201" s="22" t="s">
         <v>1146</v>
       </c>
@@ -19169,7 +19168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="75">
       <c r="A202" s="22" t="s">
         <v>1149</v>
       </c>
@@ -19225,7 +19224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="75">
       <c r="A203" s="22" t="s">
         <v>1151</v>
       </c>
@@ -19281,7 +19280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="75">
       <c r="A204" s="22" t="s">
         <v>1154</v>
       </c>
@@ -19337,7 +19336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="75">
       <c r="A205" s="22" t="s">
         <v>1157</v>
       </c>
@@ -19393,7 +19392,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="75">
       <c r="A206" s="22" t="s">
         <v>1160</v>
       </c>
@@ -19449,7 +19448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="75">
       <c r="A207" s="22" t="s">
         <v>1163</v>
       </c>
@@ -19505,7 +19504,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="75">
       <c r="A208" s="22" t="s">
         <v>1166</v>
       </c>
@@ -19561,7 +19560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="75">
       <c r="A209" s="22" t="s">
         <v>1169</v>
       </c>
@@ -19617,7 +19616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="60">
       <c r="A210" s="22" t="s">
         <v>1172</v>
       </c>
@@ -19673,7 +19672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="60">
       <c r="A211" s="22" t="s">
         <v>1176</v>
       </c>
@@ -19729,7 +19728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="60">
       <c r="A212" s="22" t="s">
         <v>1179</v>
       </c>
@@ -19785,7 +19784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="60">
       <c r="A213" s="22" t="s">
         <v>1182</v>
       </c>
@@ -19841,7 +19840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="60">
       <c r="A214" s="22" t="s">
         <v>1185</v>
       </c>
@@ -19897,7 +19896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="60">
       <c r="A215" s="22" t="s">
         <v>1188</v>
       </c>
@@ -19953,7 +19952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="60">
       <c r="A216" s="22" t="s">
         <v>1191</v>
       </c>
@@ -20009,7 +20008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ht="60">
       <c r="A217" s="22" t="s">
         <v>1194</v>
       </c>
@@ -20065,7 +20064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ht="60">
       <c r="A218" s="22" t="s">
         <v>1197</v>
       </c>
@@ -20121,7 +20120,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="60">
       <c r="A219" s="22" t="s">
         <v>1200</v>
       </c>
@@ -20177,7 +20176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="60">
       <c r="A220" s="22" t="s">
         <v>1203</v>
       </c>
@@ -20233,7 +20232,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="60">
       <c r="A221" s="22" t="s">
         <v>1206</v>
       </c>
@@ -20289,7 +20288,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="60">
       <c r="A222" s="22" t="s">
         <v>1209</v>
       </c>
@@ -20345,7 +20344,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ht="195">
       <c r="A223" s="22" t="s">
         <v>1212</v>
       </c>
@@ -20401,7 +20400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ht="195">
       <c r="A224" s="22" t="s">
         <v>1215</v>
       </c>
@@ -20457,7 +20456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="195">
       <c r="A225" s="22" t="s">
         <v>1218</v>
       </c>
@@ -20513,7 +20512,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="75">
       <c r="A226" s="22" t="s">
         <v>1220</v>
       </c>
@@ -20569,7 +20568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="75">
       <c r="A227" s="22" t="s">
         <v>1224</v>
       </c>
@@ -20625,7 +20624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="75">
       <c r="A228" s="22" t="s">
         <v>1227</v>
       </c>
@@ -20681,7 +20680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" ht="75">
       <c r="A229" s="22" t="s">
         <v>1230</v>
       </c>
@@ -20737,7 +20736,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="75">
       <c r="A230" s="22" t="s">
         <v>1233</v>
       </c>
@@ -20793,7 +20792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="75">
       <c r="A231" s="22" t="s">
         <v>1236</v>
       </c>
@@ -20849,7 +20848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="75">
       <c r="A232" s="22" t="s">
         <v>1239</v>
       </c>
@@ -20905,7 +20904,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="75">
       <c r="A233" s="22" t="s">
         <v>1242</v>
       </c>
@@ -20961,7 +20960,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="75">
       <c r="A234" s="22" t="s">
         <v>1245</v>
       </c>
@@ -21017,7 +21016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ht="75">
       <c r="A235" s="22" t="s">
         <v>1248</v>
       </c>
@@ -21073,7 +21072,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="75">
       <c r="A236" s="22" t="s">
         <v>1251</v>
       </c>
@@ -21129,7 +21128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ht="60">
       <c r="A237" s="22" t="s">
         <v>1254</v>
       </c>
@@ -21185,7 +21184,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="60">
       <c r="A238" s="22" t="s">
         <v>1257</v>
       </c>
@@ -21241,7 +21240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ht="345">
       <c r="A239" s="22" t="s">
         <v>1259</v>
       </c>
@@ -21297,7 +21296,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="345">
       <c r="A240" s="22" t="s">
         <v>1262</v>
       </c>
@@ -21353,7 +21352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="345">
       <c r="A241" s="22" t="s">
         <v>1265</v>
       </c>
@@ -21409,7 +21408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="75">
       <c r="A242" s="22" t="s">
         <v>1268</v>
       </c>
@@ -21465,7 +21464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="60">
       <c r="A243" s="22" t="s">
         <v>1272</v>
       </c>
@@ -21521,7 +21520,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ht="60">
       <c r="A244" s="22" t="s">
         <v>1275</v>
       </c>
@@ -21577,7 +21576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" ht="60">
       <c r="A245" s="22" t="s">
         <v>1278</v>
       </c>
@@ -21633,7 +21632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" ht="60">
       <c r="A246" s="22" t="s">
         <v>1281</v>
       </c>
@@ -21689,7 +21688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" ht="75">
       <c r="A247" s="22" t="s">
         <v>1284</v>
       </c>
@@ -21745,7 +21744,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" ht="75">
       <c r="A248" s="22" t="s">
         <v>1287</v>
       </c>
@@ -21801,7 +21800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" ht="60">
       <c r="A249" s="22" t="s">
         <v>1292</v>
       </c>
@@ -21857,7 +21856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" ht="60">
       <c r="A250" s="22" t="s">
         <v>1296</v>
       </c>
@@ -21913,7 +21912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" ht="60">
       <c r="A251" s="22" t="s">
         <v>1299</v>
       </c>
@@ -21969,7 +21968,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ht="60">
       <c r="A252" s="22" t="s">
         <v>1302</v>
       </c>
@@ -22025,7 +22024,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" ht="60">
       <c r="A253" s="22" t="s">
         <v>1305</v>
       </c>
@@ -22081,7 +22080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" ht="60">
       <c r="A254" s="22" t="s">
         <v>1308</v>
       </c>
@@ -22137,7 +22136,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" ht="60">
       <c r="A255" s="22" t="s">
         <v>1311</v>
       </c>
@@ -22193,7 +22192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ht="60">
       <c r="A256" s="22" t="s">
         <v>1314</v>
       </c>
@@ -22249,7 +22248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" ht="60">
       <c r="A257" s="22" t="s">
         <v>1317</v>
       </c>
@@ -22305,7 +22304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" ht="60">
       <c r="A258" s="22" t="s">
         <v>1320</v>
       </c>
@@ -22361,7 +22360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" ht="60">
       <c r="A259" s="22" t="s">
         <v>1322</v>
       </c>
@@ -22417,7 +22416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" ht="60">
       <c r="A260" s="22" t="s">
         <v>1324</v>
       </c>
@@ -22473,7 +22472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" ht="60">
       <c r="A261" s="22" t="s">
         <v>1326</v>
       </c>
@@ -22529,7 +22528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" ht="60">
       <c r="A262" s="22" t="s">
         <v>1328</v>
       </c>
@@ -22585,7 +22584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" ht="60">
       <c r="A263" s="22" t="s">
         <v>1331</v>
       </c>
@@ -22641,7 +22640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" ht="60">
       <c r="A264" s="22" t="s">
         <v>1333</v>
       </c>
@@ -22697,7 +22696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" ht="60">
       <c r="A265" s="22" t="s">
         <v>1335</v>
       </c>
@@ -22753,7 +22752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" ht="60">
       <c r="A266" s="22" t="s">
         <v>1337</v>
       </c>
@@ -22809,7 +22808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" ht="60">
       <c r="A267" s="22" t="s">
         <v>1340</v>
       </c>
@@ -22865,7 +22864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" ht="60">
       <c r="A268" s="22" t="s">
         <v>1342</v>
       </c>
@@ -22921,7 +22920,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ht="60">
       <c r="A269" s="22" t="s">
         <v>1345</v>
       </c>
@@ -22977,7 +22976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" ht="409.5">
       <c r="A270" s="22" t="s">
         <v>1348</v>
       </c>
@@ -23033,7 +23032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" ht="409.5">
       <c r="A271" s="22" t="s">
         <v>1350</v>
       </c>
@@ -23089,7 +23088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" ht="409.5">
       <c r="A272" s="22" t="s">
         <v>1352</v>
       </c>
@@ -23145,7 +23144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" ht="409.5">
       <c r="A273" s="22" t="s">
         <v>1354</v>
       </c>
@@ -23201,7 +23200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" ht="409.5">
       <c r="A274" s="22" t="s">
         <v>1356</v>
       </c>
@@ -23257,7 +23256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" ht="409.5">
       <c r="A275" s="22" t="s">
         <v>1358</v>
       </c>
@@ -23313,7 +23312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" ht="409.5">
       <c r="A276" s="22" t="s">
         <v>1359</v>
       </c>
@@ -23369,7 +23368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" ht="409.5">
       <c r="A277" s="22" t="s">
         <v>1362</v>
       </c>
@@ -23425,7 +23424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" ht="409.5">
       <c r="A278" s="22" t="s">
         <v>1364</v>
       </c>
@@ -23481,7 +23480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ht="409.5">
       <c r="A279" s="22" t="s">
         <v>1366</v>
       </c>
@@ -23537,7 +23536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ht="409.5">
       <c r="A280" s="22" t="s">
         <v>1368</v>
       </c>
@@ -23593,7 +23592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" ht="409.5">
       <c r="A281" s="22" t="s">
         <v>1370</v>
       </c>
@@ -23649,7 +23648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ht="409.5">
       <c r="A282" s="22" t="s">
         <v>1373</v>
       </c>
@@ -23705,7 +23704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ht="409.5">
       <c r="A283" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23761,7 +23760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" ht="409.5">
       <c r="A284" s="22" t="s">
         <v>1379</v>
       </c>
@@ -23817,7 +23816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" ht="409.5">
       <c r="A285" s="22" t="s">
         <v>1382</v>
       </c>
@@ -23873,7 +23872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ht="409.5">
       <c r="A286" s="22" t="s">
         <v>1385</v>
       </c>
@@ -23929,7 +23928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" ht="75">
       <c r="A287" s="22" t="s">
         <v>1388</v>
       </c>
@@ -23985,7 +23984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ht="330">
       <c r="A288" s="22" t="s">
         <v>1391</v>
       </c>
@@ -24041,7 +24040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ht="75">
       <c r="A289" s="22" t="s">
         <v>1393</v>
       </c>
@@ -24097,7 +24096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ht="60">
       <c r="A290" s="22" t="s">
         <v>1400</v>
       </c>
@@ -24153,7 +24152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ht="75">
       <c r="A291" s="22" t="s">
         <v>1403</v>
       </c>
@@ -24209,7 +24208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" ht="75">
       <c r="A292" s="22" t="s">
         <v>1406</v>
       </c>
@@ -24265,7 +24264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" ht="75">
       <c r="A293" s="22" t="s">
         <v>1409</v>
       </c>
@@ -24321,7 +24320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" ht="60">
       <c r="A294" s="22" t="s">
         <v>1412</v>
       </c>
@@ -24377,7 +24376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ht="60">
       <c r="A295" s="22" t="s">
         <v>1417</v>
       </c>
@@ -24433,7 +24432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ht="60">
       <c r="A296" s="22" t="s">
         <v>1420</v>
       </c>
@@ -24489,7 +24488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ht="60">
       <c r="A297" s="22" t="s">
         <v>1423</v>
       </c>
@@ -24545,7 +24544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ht="60">
       <c r="A298" s="22" t="s">
         <v>1425</v>
       </c>
@@ -24601,7 +24600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ht="60">
       <c r="A299" s="22" t="s">
         <v>1427</v>
       </c>
@@ -24657,7 +24656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ht="75">
       <c r="A300" s="22" t="s">
         <v>1429</v>
       </c>
@@ -24713,7 +24712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ht="60">
       <c r="A301" s="22" t="s">
         <v>1432</v>
       </c>
@@ -24769,7 +24768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ht="60">
       <c r="A302" s="22" t="s">
         <v>1435</v>
       </c>
@@ -24825,7 +24824,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ht="60">
       <c r="A303" s="22" t="s">
         <v>1438</v>
       </c>
@@ -24881,7 +24880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" ht="60">
       <c r="A304" s="22" t="s">
         <v>1440</v>
       </c>
@@ -24937,7 +24936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" ht="60">
       <c r="A305" s="22" t="s">
         <v>1442</v>
       </c>
@@ -24993,7 +24992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" ht="60">
       <c r="A306" s="22" t="s">
         <v>1444</v>
       </c>
@@ -25049,7 +25048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" ht="60">
       <c r="A307" s="22" t="s">
         <v>1446</v>
       </c>
@@ -25105,7 +25104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" ht="60">
       <c r="A308" s="22" t="s">
         <v>1448</v>
       </c>
@@ -25161,7 +25160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" ht="60">
       <c r="A309" s="22" t="s">
         <v>1450</v>
       </c>
@@ -25217,7 +25216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" ht="60">
       <c r="A310" s="22" t="s">
         <v>1452</v>
       </c>
@@ -25273,7 +25272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" ht="60">
       <c r="A311" s="22" t="s">
         <v>1454</v>
       </c>
@@ -25329,7 +25328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" ht="90">
       <c r="A312" s="22" t="s">
         <v>1456</v>
       </c>
@@ -25385,7 +25384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" ht="60">
       <c r="A313" s="22" t="s">
         <v>1459</v>
       </c>
@@ -25441,7 +25440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" ht="60">
       <c r="A314" s="22" t="s">
         <v>1462</v>
       </c>
@@ -25497,7 +25496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ht="60">
       <c r="A315" s="22" t="s">
         <v>1464</v>
       </c>
@@ -25553,7 +25552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" ht="60">
       <c r="A316" s="22" t="s">
         <v>1466</v>
       </c>
@@ -25609,7 +25608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ht="60">
       <c r="A317" s="22" t="s">
         <v>1468</v>
       </c>
@@ -25665,7 +25664,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" ht="60">
       <c r="A318" s="22" t="s">
         <v>1470</v>
       </c>
@@ -25721,7 +25720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" ht="60">
       <c r="A319" s="22" t="s">
         <v>1472</v>
       </c>
@@ -25777,7 +25776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" ht="60">
       <c r="A320" s="22" t="s">
         <v>1474</v>
       </c>
@@ -25833,7 +25832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ht="60">
       <c r="A321" s="22" t="s">
         <v>1476</v>
       </c>
@@ -25889,7 +25888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" ht="60">
       <c r="A322" s="22" t="s">
         <v>1478</v>
       </c>
@@ -25945,7 +25944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" ht="60">
       <c r="A323" s="22" t="s">
         <v>1480</v>
       </c>
@@ -26001,7 +26000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" ht="60">
       <c r="A324" s="22" t="s">
         <v>1483</v>
       </c>
@@ -26057,7 +26056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ht="60">
       <c r="A325" s="22" t="s">
         <v>1485</v>
       </c>
@@ -26113,7 +26112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" ht="210">
       <c r="A326" s="22" t="s">
         <v>1488</v>
       </c>
@@ -26169,7 +26168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" ht="210">
       <c r="A327" s="22" t="s">
         <v>1493</v>
       </c>
@@ -26225,7 +26224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ht="210">
       <c r="A328" s="22" t="s">
         <v>1496</v>
       </c>
@@ -26281,7 +26280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" ht="210">
       <c r="A329" s="22" t="s">
         <v>1497</v>
       </c>
@@ -26337,7 +26336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" ht="210">
       <c r="A330" s="22" t="s">
         <v>1498</v>
       </c>
@@ -26393,7 +26392,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" ht="210">
       <c r="A331" s="22" t="s">
         <v>1499</v>
       </c>
@@ -26449,7 +26448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" ht="210">
       <c r="A332" s="22" t="s">
         <v>1502</v>
       </c>
@@ -26505,7 +26504,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" ht="210">
       <c r="A333" s="22" t="s">
         <v>1504</v>
       </c>
@@ -26561,7 +26560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="210">
       <c r="A334" s="22" t="s">
         <v>1506</v>
       </c>
@@ -26617,7 +26616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="210">
       <c r="A335" s="22" t="s">
         <v>1508</v>
       </c>
@@ -26673,7 +26672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" ht="210">
       <c r="A336" s="22" t="s">
         <v>1510</v>
       </c>
@@ -26729,7 +26728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ht="210">
       <c r="A337" s="22" t="s">
         <v>1513</v>
       </c>
@@ -26785,7 +26784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" ht="210">
       <c r="A338" s="22" t="s">
         <v>1516</v>
       </c>
@@ -26841,7 +26840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ht="210">
       <c r="A339" s="22" t="s">
         <v>1519</v>
       </c>
@@ -26897,7 +26896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" ht="210">
       <c r="A340" s="22" t="s">
         <v>1522</v>
       </c>
@@ -26953,7 +26952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" ht="210">
       <c r="A341" s="22" t="s">
         <v>1525</v>
       </c>
@@ -27009,7 +27008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ht="210">
       <c r="A342" s="22" t="s">
         <v>1528</v>
       </c>
@@ -27065,7 +27064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" ht="210">
       <c r="A343" s="22" t="s">
         <v>1531</v>
       </c>
@@ -27121,7 +27120,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ht="210">
       <c r="A344" s="22" t="s">
         <v>1534</v>
       </c>
@@ -27177,7 +27176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="210">
       <c r="A345" s="22" t="s">
         <v>1537</v>
       </c>
@@ -27233,7 +27232,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ht="210">
       <c r="A346" s="22" t="s">
         <v>1540</v>
       </c>
@@ -27289,7 +27288,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ht="210">
       <c r="A347" s="22" t="s">
         <v>1543</v>
       </c>
@@ -27345,7 +27344,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ht="210">
       <c r="A348" s="22" t="s">
         <v>1546</v>
       </c>
@@ -27401,7 +27400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" ht="210">
       <c r="A349" s="22" t="s">
         <v>1549</v>
       </c>
@@ -27457,7 +27456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" ht="210">
       <c r="A350" s="22" t="s">
         <v>1552</v>
       </c>
@@ -27513,7 +27512,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" ht="210">
       <c r="A351" s="22" t="s">
         <v>1555</v>
       </c>
@@ -27569,7 +27568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ht="210">
       <c r="A352" s="22" t="s">
         <v>1558</v>
       </c>
@@ -27625,7 +27624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="210">
       <c r="A353" s="22" t="s">
         <v>1561</v>
       </c>
@@ -27681,7 +27680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="210">
       <c r="A354" s="22" t="s">
         <v>1564</v>
       </c>
@@ -27737,7 +27736,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="210">
       <c r="A355" s="22" t="s">
         <v>1567</v>
       </c>
@@ -27793,7 +27792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="210">
       <c r="A356" s="22" t="s">
         <v>1570</v>
       </c>
@@ -27849,7 +27848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="210">
       <c r="A357" s="22" t="s">
         <v>1573</v>
       </c>
@@ -27905,7 +27904,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="210">
       <c r="A358" s="22" t="s">
         <v>1576</v>
       </c>
@@ -27961,7 +27960,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="210">
       <c r="A359" s="22" t="s">
         <v>1579</v>
       </c>
@@ -28017,7 +28016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="210">
       <c r="A360" s="22" t="s">
         <v>1582</v>
       </c>
@@ -28073,7 +28072,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="210">
       <c r="A361" s="22" t="s">
         <v>1585</v>
       </c>
@@ -28129,7 +28128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="210">
       <c r="A362" s="22" t="s">
         <v>1588</v>
       </c>
@@ -28185,7 +28184,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="210">
       <c r="A363" s="22" t="s">
         <v>1590</v>
       </c>
@@ -28241,7 +28240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" ht="210">
       <c r="A364" s="22" t="s">
         <v>1592</v>
       </c>
@@ -28297,7 +28296,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="210">
       <c r="A365" s="22" t="s">
         <v>1594</v>
       </c>
@@ -28353,7 +28352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="210">
       <c r="A366" s="22" t="s">
         <v>1597</v>
       </c>
@@ -28409,7 +28408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="60">
       <c r="A367" s="22" t="s">
         <v>1600</v>
       </c>
@@ -28465,7 +28464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="60">
       <c r="A368" s="22" t="s">
         <v>1603</v>
       </c>
@@ -28521,7 +28520,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="60">
       <c r="A369" s="22" t="s">
         <v>1606</v>
       </c>
@@ -28577,7 +28576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="60">
       <c r="A370" s="22" t="s">
         <v>1608</v>
       </c>
@@ -28633,7 +28632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="60">
       <c r="A371" s="22" t="s">
         <v>1610</v>
       </c>
@@ -28689,7 +28688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="60">
       <c r="A372" s="22" t="s">
         <v>1612</v>
       </c>
@@ -28745,7 +28744,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ht="60">
       <c r="A373" s="22" t="s">
         <v>1614</v>
       </c>
@@ -28801,7 +28800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ht="60">
       <c r="A374" s="22" t="s">
         <v>1615</v>
       </c>
@@ -28857,7 +28856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" ht="60">
       <c r="A375" s="22" t="s">
         <v>1618</v>
       </c>
@@ -28913,7 +28912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" ht="60">
       <c r="A376" s="22" t="s">
         <v>1621</v>
       </c>
@@ -28969,7 +28968,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" ht="60">
       <c r="A377" s="22" t="s">
         <v>1624</v>
       </c>
@@ -29025,7 +29024,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ht="60">
       <c r="A378" s="22" t="s">
         <v>1627</v>
       </c>
@@ -29081,7 +29080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ht="75">
       <c r="A379" s="22" t="s">
         <v>1630</v>
       </c>
@@ -29137,7 +29136,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ht="60">
       <c r="A380" s="22" t="s">
         <v>1633</v>
       </c>
@@ -29193,7 +29192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ht="90">
       <c r="A381" s="22" t="s">
         <v>1636</v>
       </c>
@@ -29249,7 +29248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" ht="75">
       <c r="A382" s="22" t="s">
         <v>1639</v>
       </c>
@@ -29305,7 +29304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" ht="75">
       <c r="A383" s="22" t="s">
         <v>1642</v>
       </c>
@@ -29361,7 +29360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" ht="60">
       <c r="A384" s="22" t="s">
         <v>1645</v>
       </c>
@@ -29417,7 +29416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" ht="60">
       <c r="A385" s="22" t="s">
         <v>1648</v>
       </c>
@@ -29473,7 +29472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="386" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:18" ht="60">
       <c r="A386" s="22" t="s">
         <v>1651</v>
       </c>
@@ -29529,7 +29528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" ht="60">
       <c r="A387" s="22" t="s">
         <v>1654</v>
       </c>
@@ -29585,7 +29584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" ht="60">
       <c r="A388" s="22" t="s">
         <v>1657</v>
       </c>
@@ -29641,7 +29640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ht="60">
       <c r="A389" s="22" t="s">
         <v>1661</v>
       </c>
@@ -29697,7 +29696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ht="60">
       <c r="A390" s="22" t="s">
         <v>1664</v>
       </c>
@@ -29753,7 +29752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ht="60">
       <c r="A391" s="22" t="s">
         <v>1667</v>
       </c>
@@ -29809,7 +29808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ht="60">
       <c r="A392" s="22" t="s">
         <v>1670</v>
       </c>
@@ -29865,7 +29864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ht="60">
       <c r="A393" s="22" t="s">
         <v>1673</v>
       </c>
@@ -29921,7 +29920,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" ht="60">
       <c r="A394" s="22" t="s">
         <v>1676</v>
       </c>
@@ -29977,7 +29976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" ht="60">
       <c r="A395" s="22" t="s">
         <v>1679</v>
       </c>
@@ -30033,7 +30032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" ht="60">
       <c r="A396" s="22" t="s">
         <v>1682</v>
       </c>
@@ -30089,7 +30088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" ht="75">
       <c r="A397" s="22" t="s">
         <v>1685</v>
       </c>
@@ -30145,7 +30144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" ht="60">
       <c r="A398" s="22" t="s">
         <v>1688</v>
       </c>
@@ -30201,7 +30200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" ht="60">
       <c r="A399" s="22" t="s">
         <v>1690</v>
       </c>
@@ -30257,7 +30256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" ht="60">
       <c r="A400" s="22" t="s">
         <v>1692</v>
       </c>
@@ -30313,7 +30312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" ht="75">
       <c r="A401" s="22" t="s">
         <v>1695</v>
       </c>
@@ -30369,7 +30368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="402" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" ht="75">
       <c r="A402" s="22" t="s">
         <v>1698</v>
       </c>
@@ -30425,7 +30424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" ht="60">
       <c r="A403" s="22" t="s">
         <v>1701</v>
       </c>
@@ -30481,7 +30480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" ht="60">
       <c r="A404" s="22" t="s">
         <v>1704</v>
       </c>
@@ -30537,7 +30536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" ht="60">
       <c r="A405" s="22" t="s">
         <v>1707</v>
       </c>
@@ -30593,7 +30592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" ht="60">
       <c r="A406" s="22" t="s">
         <v>1710</v>
       </c>
@@ -30649,7 +30648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" ht="60">
       <c r="A407" s="22" t="s">
         <v>1713</v>
       </c>
@@ -30705,7 +30704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" ht="60">
       <c r="A408" s="22" t="s">
         <v>1716</v>
       </c>
@@ -30761,7 +30760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" ht="60">
       <c r="A409" s="22" t="s">
         <v>1719</v>
       </c>
@@ -30817,7 +30816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" ht="195">
       <c r="A410" s="22" t="s">
         <v>1722</v>
       </c>
@@ -30873,7 +30872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" ht="60">
       <c r="A411" s="22" t="s">
         <v>1725</v>
       </c>
@@ -30929,7 +30928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" ht="60">
       <c r="A412" s="22" t="s">
         <v>1728</v>
       </c>
@@ -30985,7 +30984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" ht="60">
       <c r="A413" s="22" t="s">
         <v>1731</v>
       </c>
@@ -31041,7 +31040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" ht="60">
       <c r="A414" s="22" t="s">
         <v>1735</v>
       </c>
@@ -31097,7 +31096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" ht="60">
       <c r="A415" s="22" t="s">
         <v>1737</v>
       </c>
@@ -31153,7 +31152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" ht="60">
       <c r="A416" s="22" t="s">
         <v>1739</v>
       </c>
@@ -31209,7 +31208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" ht="60">
       <c r="A417" s="22" t="s">
         <v>1742</v>
       </c>
@@ -31265,7 +31264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" ht="60">
       <c r="A418" s="22" t="s">
         <v>1745</v>
       </c>
@@ -31321,7 +31320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" ht="60">
       <c r="A419" s="22" t="s">
         <v>1748</v>
       </c>
@@ -31377,7 +31376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" ht="60">
       <c r="A420" s="22" t="s">
         <v>1751</v>
       </c>
@@ -31433,7 +31432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" ht="75">
       <c r="A421" s="22" t="s">
         <v>1753</v>
       </c>
@@ -31489,7 +31488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" ht="75">
       <c r="A422" s="22" t="s">
         <v>1756</v>
       </c>
@@ -31545,7 +31544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" ht="75">
       <c r="A423" s="22" t="s">
         <v>1759</v>
       </c>
@@ -31601,7 +31600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" ht="75">
       <c r="A424" s="22" t="s">
         <v>1762</v>
       </c>
@@ -31657,7 +31656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" ht="409.5">
       <c r="A425" s="22" t="s">
         <v>1765</v>
       </c>
@@ -31713,7 +31712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" ht="60">
       <c r="A426" s="22" t="s">
         <v>1768</v>
       </c>
@@ -31769,7 +31768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" ht="60">
       <c r="A427" s="22" t="s">
         <v>1772</v>
       </c>
@@ -31825,7 +31824,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" ht="60">
       <c r="A428" s="22" t="s">
         <v>1775</v>
       </c>
@@ -31881,7 +31880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" ht="60">
       <c r="A429" s="22" t="s">
         <v>1778</v>
       </c>
@@ -31937,7 +31936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="75">
       <c r="A430" s="22" t="s">
         <v>1781</v>
       </c>
@@ -31993,7 +31992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="75">
       <c r="A431" s="22" t="s">
         <v>1784</v>
       </c>
@@ -32049,7 +32048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="60">
       <c r="A432" s="22" t="s">
         <v>1787</v>
       </c>
@@ -32105,7 +32104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="60">
       <c r="A433" s="22" t="s">
         <v>1790</v>
       </c>
@@ -32161,7 +32160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="60">
       <c r="A434" s="22" t="s">
         <v>1793</v>
       </c>
@@ -32217,7 +32216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="330" hidden="1">
       <c r="A435" s="22" t="s">
         <v>189</v>
       </c>
@@ -32273,7 +32272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="330" hidden="1">
       <c r="A436" s="22" t="s">
         <v>195</v>
       </c>
@@ -32329,7 +32328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" ht="105" hidden="1">
       <c r="A437" s="22" t="s">
         <v>310</v>
       </c>
@@ -32385,7 +32384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="105" hidden="1">
       <c r="A438" s="22" t="s">
         <v>313</v>
       </c>
@@ -32441,7 +32440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="105" hidden="1">
       <c r="A439" s="22" t="s">
         <v>315</v>
       </c>
@@ -32497,7 +32496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="105" hidden="1">
       <c r="A440" s="22" t="s">
         <v>318</v>
       </c>
@@ -32553,7 +32552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="60" hidden="1">
       <c r="A441" s="22" t="s">
         <v>353</v>
       </c>
@@ -32609,7 +32608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="60" hidden="1">
       <c r="A442" s="22" t="s">
         <v>356</v>
       </c>
@@ -32665,7 +32664,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="60" hidden="1">
       <c r="A443" s="22" t="s">
         <v>361</v>
       </c>
@@ -32721,7 +32720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="90" hidden="1">
       <c r="A444" s="22" t="s">
         <v>433</v>
       </c>
@@ -32777,7 +32776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="90" hidden="1">
       <c r="A445" s="22" t="s">
         <v>436</v>
       </c>
@@ -32833,7 +32832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="75" hidden="1">
       <c r="A446" s="22" t="s">
         <v>506</v>
       </c>
@@ -32889,7 +32888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="75" hidden="1">
       <c r="A447" s="22" t="s">
         <v>509</v>
       </c>
@@ -32945,7 +32944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="60" hidden="1">
       <c r="A448" s="23" t="s">
         <v>512</v>
       </c>
@@ -33001,7 +33000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="60" hidden="1">
       <c r="A449" s="22" t="s">
         <v>549</v>
       </c>
@@ -33057,7 +33056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="60" hidden="1">
       <c r="A450" s="22" t="s">
         <v>551</v>
       </c>
@@ -33113,7 +33112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="60" hidden="1">
       <c r="A451" s="22" t="s">
         <v>553</v>
       </c>
@@ -33169,7 +33168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="60" hidden="1">
       <c r="A452" s="22" t="s">
         <v>555</v>
       </c>
@@ -33225,7 +33224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="60" hidden="1">
       <c r="A453" s="22" t="s">
         <v>557</v>
       </c>
@@ -33281,7 +33280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="60" hidden="1">
       <c r="A454" s="22" t="s">
         <v>559</v>
       </c>
@@ -33337,7 +33336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="60" hidden="1">
       <c r="A455" s="22" t="s">
         <v>561</v>
       </c>
@@ -33393,7 +33392,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="60" hidden="1">
       <c r="A456" s="22" t="s">
         <v>568</v>
       </c>
@@ -33449,7 +33448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="60" hidden="1">
       <c r="A457" s="22" t="s">
         <v>571</v>
       </c>
@@ -33505,7 +33504,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="345" hidden="1">
       <c r="A458" s="22" t="s">
         <v>679</v>
       </c>
@@ -33561,7 +33560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="345" hidden="1">
       <c r="A459" s="22" t="s">
         <v>682</v>
       </c>
@@ -33617,7 +33616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" ht="150" hidden="1">
       <c r="A460" s="22" t="s">
         <v>747</v>
       </c>
@@ -33673,7 +33672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="60" hidden="1">
       <c r="A461" s="22" t="s">
         <v>346</v>
       </c>
@@ -33729,7 +33728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="60" hidden="1">
       <c r="A462" s="22" t="s">
         <v>350</v>
       </c>
@@ -33785,7 +33784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="60" hidden="1">
       <c r="A463" s="22" t="s">
         <v>359</v>
       </c>
@@ -33841,7 +33840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="345" hidden="1">
       <c r="A464" s="22" t="s">
         <v>677</v>
       </c>
@@ -33897,7 +33896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="409.5" hidden="1">
       <c r="A465" s="22" t="s">
         <v>862</v>
       </c>
@@ -33953,7 +33952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="409.5" hidden="1">
       <c r="A466" s="22" t="s">
         <v>864</v>
       </c>
@@ -34009,7 +34008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="409.5" hidden="1">
       <c r="A467" s="22" t="s">
         <v>876</v>
       </c>
@@ -34065,7 +34064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="60" hidden="1">
       <c r="A468" s="22" t="s">
         <v>887</v>
       </c>
@@ -34121,7 +34120,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:18" ht="60" hidden="1">
       <c r="A469" s="22" t="s">
         <v>888</v>
       </c>
@@ -34177,7 +34176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:18" ht="60" hidden="1">
       <c r="A470" s="22" t="s">
         <v>891</v>
       </c>
@@ -34233,7 +34232,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:18" ht="60" hidden="1">
       <c r="A471" s="22" t="s">
         <v>899</v>
       </c>
@@ -34289,7 +34288,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="345" hidden="1">
       <c r="A472" s="22" t="s">
         <v>732</v>
       </c>
@@ -34345,7 +34344,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="150" hidden="1">
       <c r="A473" s="22" t="s">
         <v>741</v>
       </c>
@@ -34401,7 +34400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="150" hidden="1">
       <c r="A474" s="22" t="s">
         <v>743</v>
       </c>
@@ -34457,7 +34456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="60" hidden="1">
       <c r="A475" s="22" t="s">
         <v>782</v>
       </c>
@@ -34513,7 +34512,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="60" hidden="1">
       <c r="A476" s="22" t="s">
         <v>784</v>
       </c>
@@ -34569,7 +34568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="60" hidden="1">
       <c r="A477" s="22" t="s">
         <v>785</v>
       </c>
@@ -34625,7 +34624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="409.5" hidden="1">
       <c r="A478" s="22" t="s">
         <v>822</v>
       </c>
@@ -34681,7 +34680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="409.5" hidden="1">
       <c r="A479" s="22" t="s">
         <v>824</v>
       </c>
@@ -34737,7 +34736,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="409.5" hidden="1">
       <c r="A480" s="22" t="s">
         <v>826</v>
       </c>
@@ -34793,7 +34792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="409.5" hidden="1">
       <c r="A481" s="22" t="s">
         <v>828</v>
       </c>
@@ -34849,7 +34848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="409.5" hidden="1">
       <c r="A482" s="22" t="s">
         <v>830</v>
       </c>
@@ -34905,7 +34904,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="409.5" hidden="1">
       <c r="A483" s="22" t="s">
         <v>837</v>
       </c>
@@ -34961,7 +34960,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="409.5" hidden="1">
       <c r="A484" s="22" t="s">
         <v>840</v>
       </c>
@@ -35017,7 +35016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="409.5" hidden="1">
       <c r="A485" s="22" t="s">
         <v>843</v>
       </c>
@@ -35073,7 +35072,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="409.5" hidden="1">
       <c r="A486" s="22" t="s">
         <v>846</v>
       </c>
@@ -35129,7 +35128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="409.5" hidden="1">
       <c r="A487" s="22" t="s">
         <v>849</v>
       </c>
@@ -35185,7 +35184,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="60" hidden="1">
       <c r="A488" s="22" t="s">
         <v>524</v>
       </c>
@@ -35241,7 +35240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="60" hidden="1">
       <c r="A489" s="22" t="s">
         <v>527</v>
       </c>
@@ -35297,7 +35296,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="60" hidden="1">
       <c r="A490" s="22" t="s">
         <v>529</v>
       </c>
@@ -35353,7 +35352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="60" hidden="1">
       <c r="A491" s="22" t="s">
         <v>532</v>
       </c>
@@ -35409,7 +35408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="60" hidden="1">
       <c r="A492" s="22" t="s">
         <v>535</v>
       </c>
@@ -35465,7 +35464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="60" hidden="1">
       <c r="A493" s="22" t="s">
         <v>538</v>
       </c>
@@ -35521,7 +35520,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="60" hidden="1">
       <c r="A494" s="22" t="s">
         <v>541</v>
       </c>
@@ -35577,7 +35576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="60" hidden="1">
       <c r="A495" s="22" t="s">
         <v>544</v>
       </c>
@@ -35633,7 +35632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="60" hidden="1">
       <c r="A496" s="22" t="s">
         <v>547</v>
       </c>
@@ -35689,7 +35688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="345" hidden="1">
       <c r="A497" s="22" t="s">
         <v>620</v>
       </c>
@@ -35745,7 +35744,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="345" hidden="1">
       <c r="A498" s="22" t="s">
         <v>622</v>
       </c>
@@ -35801,7 +35800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="345" hidden="1">
       <c r="A499" s="22" t="s">
         <v>625</v>
       </c>
@@ -35857,7 +35856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="345" hidden="1">
       <c r="A500" s="22" t="s">
         <v>626</v>
       </c>
@@ -35913,7 +35912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="345" hidden="1">
       <c r="A501" s="22" t="s">
         <v>629</v>
       </c>
@@ -35969,7 +35968,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" ht="345" hidden="1">
       <c r="A502" s="22" t="s">
         <v>632</v>
       </c>
@@ -36025,7 +36024,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="345" hidden="1">
       <c r="A503" s="22" t="s">
         <v>636</v>
       </c>
@@ -36081,7 +36080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="345" hidden="1">
       <c r="A504" s="22" t="s">
         <v>666</v>
       </c>
@@ -36137,7 +36136,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="345" hidden="1">
       <c r="A505" s="22" t="s">
         <v>669</v>
       </c>
@@ -36193,7 +36192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:18" ht="345" hidden="1">
       <c r="A506" s="22" t="s">
         <v>672</v>
       </c>
@@ -36249,7 +36248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="345" hidden="1">
       <c r="A507" s="22" t="s">
         <v>674</v>
       </c>
@@ -36305,7 +36304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="345" hidden="1">
       <c r="A508" s="22" t="s">
         <v>676</v>
       </c>
@@ -36361,7 +36360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="60" hidden="1">
       <c r="A509" s="22" t="s">
         <v>488</v>
       </c>
@@ -36417,7 +36416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="60" hidden="1">
       <c r="A510" s="22" t="s">
         <v>491</v>
       </c>
@@ -36473,7 +36472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:18" ht="60" hidden="1">
       <c r="A511" s="22" t="s">
         <v>497</v>
       </c>
@@ -36529,7 +36528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:18" ht="60" hidden="1">
       <c r="A512" s="22" t="s">
         <v>516</v>
       </c>
@@ -36585,7 +36584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" ht="60" hidden="1">
       <c r="A513" s="22" t="s">
         <v>519</v>
       </c>
@@ -36641,7 +36640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="60" hidden="1">
       <c r="A514" s="22" t="s">
         <v>521</v>
       </c>
@@ -36697,7 +36696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="60" hidden="1">
       <c r="A515" s="22" t="s">
         <v>372</v>
       </c>
@@ -36753,7 +36752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="60" hidden="1">
       <c r="A516" s="22" t="s">
         <v>388</v>
       </c>
@@ -36809,7 +36808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="60" hidden="1">
       <c r="A517" s="22" t="s">
         <v>469</v>
       </c>
@@ -36865,7 +36864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="60" hidden="1">
       <c r="A518" s="22" t="s">
         <v>472</v>
       </c>
@@ -36921,7 +36920,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="60" hidden="1">
       <c r="A519" s="22" t="s">
         <v>474</v>
       </c>
@@ -36977,7 +36976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="60" hidden="1">
       <c r="A520" s="22" t="s">
         <v>476</v>
       </c>
@@ -37033,7 +37032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="60" hidden="1">
       <c r="A521" s="22" t="s">
         <v>479</v>
       </c>
@@ -37089,7 +37088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="60" hidden="1">
       <c r="A522" s="22" t="s">
         <v>482</v>
       </c>
@@ -37145,7 +37144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="60" hidden="1">
       <c r="A523" s="22" t="s">
         <v>485</v>
       </c>
@@ -37201,7 +37200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="345" hidden="1">
       <c r="A524" s="22" t="s">
         <v>635</v>
       </c>
@@ -37257,7 +37256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="525" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="345" hidden="1">
       <c r="A525" s="22" t="s">
         <v>639</v>
       </c>
@@ -37313,7 +37312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="345" hidden="1">
       <c r="A526" s="22" t="s">
         <v>642</v>
       </c>
@@ -37369,7 +37368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="345" hidden="1">
       <c r="A527" s="22" t="s">
         <v>643</v>
       </c>
@@ -37425,7 +37424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="345" hidden="1">
       <c r="A528" s="22" t="s">
         <v>646</v>
       </c>
@@ -37481,7 +37480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="345" hidden="1">
       <c r="A529" s="22" t="s">
         <v>648</v>
       </c>
@@ -37537,7 +37536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="345" hidden="1">
       <c r="A530" s="22" t="s">
         <v>651</v>
       </c>
@@ -37593,7 +37592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="531" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="345" hidden="1">
       <c r="A531" s="22" t="s">
         <v>654</v>
       </c>
@@ -37649,7 +37648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="345" hidden="1">
       <c r="A532" s="22" t="s">
         <v>657</v>
       </c>
@@ -37705,7 +37704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="533" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="345" hidden="1">
       <c r="A533" s="22" t="s">
         <v>659</v>
       </c>
@@ -37761,7 +37760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="345" hidden="1">
       <c r="A534" s="22" t="s">
         <v>661</v>
       </c>
@@ -37817,7 +37816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="345" hidden="1">
       <c r="A535" s="22" t="s">
         <v>663</v>
       </c>
@@ -37873,7 +37872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="135" hidden="1">
       <c r="A536" s="22" t="s">
         <v>694</v>
       </c>
@@ -37929,7 +37928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="537" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="135" hidden="1">
       <c r="A537" s="22" t="s">
         <v>697</v>
       </c>
@@ -37985,7 +37984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="150" hidden="1">
       <c r="A538" s="22" t="s">
         <v>735</v>
       </c>
@@ -38041,7 +38040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="150" hidden="1">
       <c r="A539" s="22" t="s">
         <v>739</v>
       </c>
@@ -38097,7 +38096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="60" hidden="1">
       <c r="A540" s="22" t="s">
         <v>386</v>
       </c>
@@ -38153,7 +38152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="60" hidden="1">
       <c r="A541" s="22" t="s">
         <v>394</v>
       </c>
@@ -38209,7 +38208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="60" hidden="1">
       <c r="A542" s="22" t="s">
         <v>397</v>
       </c>
@@ -38265,7 +38264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="60" hidden="1">
       <c r="A543" s="22" t="s">
         <v>399</v>
       </c>
@@ -38321,7 +38320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="544" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" ht="60" hidden="1">
       <c r="A544" s="22" t="s">
         <v>402</v>
       </c>
@@ -38377,7 +38376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="60" hidden="1">
       <c r="A545" s="22" t="s">
         <v>405</v>
       </c>
@@ -38433,7 +38432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="60" hidden="1">
       <c r="A546" s="22" t="s">
         <v>408</v>
       </c>
@@ -38489,7 +38488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="75" hidden="1">
       <c r="A547" s="22" t="s">
         <v>411</v>
       </c>
@@ -38545,7 +38544,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="90" hidden="1">
       <c r="A548" s="22" t="s">
         <v>423</v>
       </c>
@@ -38601,7 +38600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="549" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" ht="90" hidden="1">
       <c r="A549" s="22" t="s">
         <v>428</v>
       </c>
@@ -38657,7 +38656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" ht="60" hidden="1">
       <c r="A550" s="22" t="s">
         <v>451</v>
       </c>
@@ -38713,7 +38712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" ht="60" hidden="1">
       <c r="A551" s="22" t="s">
         <v>454</v>
       </c>
@@ -38769,7 +38768,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" ht="330" hidden="1">
       <c r="A552" s="22" t="s">
         <v>187</v>
       </c>
@@ -38825,7 +38824,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="553" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:18" ht="60" hidden="1">
       <c r="A553" s="22" t="s">
         <v>331</v>
       </c>
@@ -38881,7 +38880,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="554" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:18" ht="60" hidden="1">
       <c r="A554" s="22" t="s">
         <v>336</v>
       </c>
@@ -38937,7 +38936,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="555" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:18" ht="60" hidden="1">
       <c r="A555" s="22" t="s">
         <v>364</v>
       </c>
@@ -38993,7 +38992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="556" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:18" ht="60" hidden="1">
       <c r="A556" s="22" t="s">
         <v>367</v>
       </c>
@@ -39049,7 +39048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="60" hidden="1">
       <c r="A557" s="22" t="s">
         <v>370</v>
       </c>
@@ -39105,7 +39104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="60" hidden="1">
       <c r="A558" s="22" t="s">
         <v>374</v>
       </c>
@@ -39161,7 +39160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="60" hidden="1">
       <c r="A559" s="22" t="s">
         <v>376</v>
       </c>
@@ -39217,7 +39216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="60" hidden="1">
       <c r="A560" s="22" t="s">
         <v>379</v>
       </c>
@@ -39273,7 +39272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="60" hidden="1">
       <c r="A561" s="22" t="s">
         <v>382</v>
       </c>
@@ -39329,7 +39328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="60" hidden="1">
       <c r="A562" s="22" t="s">
         <v>384</v>
       </c>
@@ -39385,7 +39384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="60" hidden="1">
       <c r="A563" s="22" t="s">
         <v>391</v>
       </c>
@@ -39441,7 +39440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="60" hidden="1">
       <c r="A564" s="22" t="s">
         <v>325</v>
       </c>
@@ -39497,7 +39496,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="60" hidden="1">
       <c r="A565" s="22" t="s">
         <v>329</v>
       </c>
@@ -39553,7 +39552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="60" hidden="1">
       <c r="A566" s="22" t="s">
         <v>321</v>
       </c>
@@ -39609,7 +39608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="567" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="60" hidden="1">
       <c r="A567" s="22" t="s">
         <v>327</v>
       </c>
@@ -39665,7 +39664,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="60" hidden="1">
       <c r="A568" s="22" t="s">
         <v>333</v>
       </c>
@@ -39721,7 +39720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="60" hidden="1">
       <c r="A569" s="22" t="s">
         <v>339</v>
       </c>
@@ -39777,7 +39776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="75" hidden="1">
       <c r="A570" s="22" t="s">
         <v>105</v>
       </c>
@@ -39833,7 +39832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="75" hidden="1">
       <c r="A571" s="22" t="s">
         <v>118</v>
       </c>
@@ -39889,7 +39888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="75" hidden="1">
       <c r="A572" s="22" t="s">
         <v>130</v>
       </c>
@@ -39945,7 +39944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="573" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="75" hidden="1">
       <c r="A573" s="22" t="s">
         <v>164</v>
       </c>
@@ -40001,7 +40000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="330" hidden="1">
       <c r="A574" s="22" t="s">
         <v>177</v>
       </c>
@@ -40057,7 +40056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="575" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="330" hidden="1">
       <c r="A575" s="22" t="s">
         <v>179</v>
       </c>
@@ -40113,7 +40112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="330" hidden="1">
       <c r="A576" s="22" t="s">
         <v>197</v>
       </c>
@@ -40169,7 +40168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="330" hidden="1">
       <c r="A577" s="22" t="s">
         <v>199</v>
       </c>
@@ -40225,7 +40224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="75" hidden="1">
       <c r="A578" s="21" t="s">
         <v>18</v>
       </c>
@@ -40281,7 +40280,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="75" hidden="1">
       <c r="A579" s="21" t="s">
         <v>33</v>
       </c>
@@ -40337,7 +40336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="105" hidden="1">
       <c r="A580" s="21" t="s">
         <v>35</v>
       </c>
@@ -40393,7 +40392,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="75" hidden="1">
       <c r="A581" s="21" t="s">
         <v>43</v>
       </c>
@@ -40449,7 +40448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="75" hidden="1">
       <c r="A582" s="21" t="s">
         <v>47</v>
       </c>
@@ -40505,7 +40504,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="75" hidden="1">
       <c r="A583" s="21" t="s">
         <v>50</v>
       </c>
@@ -40561,7 +40560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="75" hidden="1">
       <c r="A584" s="22" t="s">
         <v>53</v>
       </c>
@@ -40617,7 +40616,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="585" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="75" hidden="1">
       <c r="A585" s="22" t="s">
         <v>55</v>
       </c>
@@ -40673,7 +40672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="586" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" ht="75" hidden="1">
       <c r="A586" s="22" t="s">
         <v>57</v>
       </c>
@@ -40729,7 +40728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="587" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="75" hidden="1">
       <c r="A587" s="22" t="s">
         <v>59</v>
       </c>
@@ -40785,7 +40784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="75" hidden="1">
       <c r="A588" s="22" t="s">
         <v>61</v>
       </c>
@@ -40841,7 +40840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="75" hidden="1">
       <c r="A589" s="22" t="s">
         <v>66</v>
       </c>
@@ -40897,7 +40896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="75" hidden="1">
       <c r="A590" s="22" t="s">
         <v>68</v>
       </c>
@@ -40953,7 +40952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="591" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="195" hidden="1">
       <c r="A591" s="22" t="s">
         <v>71</v>
       </c>
@@ -41009,7 +41008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="195" hidden="1">
       <c r="A592" s="22" t="s">
         <v>75</v>
       </c>
@@ -41065,7 +41064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="195" hidden="1">
       <c r="A593" s="22" t="s">
         <v>77</v>
       </c>
@@ -41121,7 +41120,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="195" hidden="1">
       <c r="A594" s="22" t="s">
         <v>80</v>
       </c>
@@ -41177,7 +41176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="595" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:18" ht="195" hidden="1">
       <c r="A595" s="22" t="s">
         <v>84</v>
       </c>
@@ -41233,7 +41232,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="596" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:18" ht="195" hidden="1">
       <c r="A596" s="22" t="s">
         <v>87</v>
       </c>
@@ -41289,7 +41288,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="597" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:18" ht="195" hidden="1">
       <c r="A597" s="22" t="s">
         <v>89</v>
       </c>
@@ -41345,7 +41344,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="598" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="195" hidden="1">
       <c r="A598" s="22" t="s">
         <v>91</v>
       </c>
@@ -41401,7 +41400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="195" hidden="1">
       <c r="A599" s="22" t="s">
         <v>93</v>
       </c>
@@ -41457,7 +41456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="195" hidden="1">
       <c r="A600" s="22" t="s">
         <v>95</v>
       </c>
@@ -41513,7 +41512,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="195" hidden="1">
       <c r="A601" s="22" t="s">
         <v>97</v>
       </c>
@@ -41569,7 +41568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="75" hidden="1">
       <c r="A602" s="22" t="s">
         <v>108</v>
       </c>
@@ -41625,7 +41624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="75" hidden="1">
       <c r="A603" s="22" t="s">
         <v>110</v>
       </c>
@@ -41681,7 +41680,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="75" hidden="1">
       <c r="A604" s="22" t="s">
         <v>112</v>
       </c>
@@ -41737,7 +41736,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="75" hidden="1">
       <c r="A605" s="22" t="s">
         <v>114</v>
       </c>
@@ -41793,7 +41792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="606" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:18" ht="75" hidden="1">
       <c r="A606" s="22" t="s">
         <v>116</v>
       </c>
@@ -41849,7 +41848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="75" hidden="1">
       <c r="A607" s="22" t="s">
         <v>120</v>
       </c>
@@ -41905,7 +41904,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="75" hidden="1">
       <c r="A608" s="22" t="s">
         <v>125</v>
       </c>
@@ -41961,7 +41960,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" ht="75" hidden="1">
       <c r="A609" s="22" t="s">
         <v>127</v>
       </c>
@@ -42017,7 +42016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:18" ht="75" hidden="1">
       <c r="A610" s="22" t="s">
         <v>136</v>
       </c>
@@ -42073,7 +42072,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" ht="75" hidden="1">
       <c r="A611" s="22" t="s">
         <v>138</v>
       </c>
@@ -42129,7 +42128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" ht="75" hidden="1">
       <c r="A612" s="22" t="s">
         <v>140</v>
       </c>
@@ -42185,7 +42184,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" ht="75" hidden="1">
       <c r="A613" s="22" t="s">
         <v>142</v>
       </c>
@@ -42241,7 +42240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" ht="75" hidden="1">
       <c r="A614" s="22" t="s">
         <v>144</v>
       </c>
@@ -42297,7 +42296,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" ht="75" hidden="1">
       <c r="A615" s="22" t="s">
         <v>146</v>
       </c>
@@ -42353,7 +42352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" ht="75" hidden="1">
       <c r="A616" s="22" t="s">
         <v>148</v>
       </c>
@@ -42409,7 +42408,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" ht="345" hidden="1">
       <c r="A617" s="22" t="s">
         <v>152</v>
       </c>
@@ -42465,7 +42464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" ht="135" hidden="1">
       <c r="A618" s="22" t="s">
         <v>156</v>
       </c>
@@ -42521,7 +42520,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:18" ht="409.5" hidden="1">
       <c r="A619" s="22" t="s">
         <v>160</v>
       </c>
@@ -42577,7 +42576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" ht="75" hidden="1">
       <c r="A620" s="22" t="s">
         <v>167</v>
       </c>
@@ -42633,7 +42632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" ht="75" hidden="1">
       <c r="A621" s="22" t="s">
         <v>169</v>
       </c>
@@ -42689,7 +42688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" ht="75" hidden="1">
       <c r="A622" s="22" t="s">
         <v>172</v>
       </c>
@@ -42745,7 +42744,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" ht="330" hidden="1">
       <c r="A623" s="22" t="s">
         <v>174</v>
       </c>
@@ -42801,7 +42800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" ht="330" hidden="1">
       <c r="A624" s="22" t="s">
         <v>181</v>
       </c>
@@ -42857,7 +42856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="330" hidden="1">
       <c r="A625" s="22" t="s">
         <v>183</v>
       </c>
@@ -42913,7 +42912,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="330" hidden="1">
       <c r="A626" s="22" t="s">
         <v>185</v>
       </c>
@@ -42969,7 +42968,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="330" hidden="1">
       <c r="A627" s="22" t="s">
         <v>191</v>
       </c>
@@ -43025,7 +43024,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:18" ht="330" hidden="1">
       <c r="A628" s="22" t="s">
         <v>193</v>
       </c>
@@ -43081,7 +43080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="629" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:18" ht="330" hidden="1">
       <c r="A629" s="22" t="s">
         <v>200</v>
       </c>
@@ -43137,7 +43136,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:18" ht="330" hidden="1">
       <c r="A630" s="22" t="s">
         <v>202</v>
       </c>
@@ -43193,7 +43192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:18" ht="330" hidden="1">
       <c r="A631" s="22" t="s">
         <v>204</v>
       </c>
@@ -43249,7 +43248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:18" ht="330" hidden="1">
       <c r="A632" s="22" t="s">
         <v>206</v>
       </c>
@@ -43305,7 +43304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="633" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:18" ht="60" hidden="1">
       <c r="A633" s="22" t="s">
         <v>208</v>
       </c>
@@ -43361,7 +43360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:18" ht="60" hidden="1">
       <c r="A634" s="22" t="s">
         <v>215</v>
       </c>
@@ -43417,7 +43416,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:18" ht="60" hidden="1">
       <c r="A635" s="22" t="s">
         <v>216</v>
       </c>
@@ -43473,7 +43472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:18" ht="60" hidden="1">
       <c r="A636" s="22" t="s">
         <v>217</v>
       </c>
@@ -43529,7 +43528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="637" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:18" ht="60" hidden="1">
       <c r="A637" s="22" t="s">
         <v>232</v>
       </c>
@@ -43585,7 +43584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="638" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:18" ht="60" hidden="1">
       <c r="A638" s="22" t="s">
         <v>234</v>
       </c>
@@ -43641,7 +43640,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="639" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:18" ht="60" hidden="1">
       <c r="A639" s="22" t="s">
         <v>237</v>
       </c>
@@ -43697,7 +43696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="640" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:18" ht="60" hidden="1">
       <c r="A640" s="22" t="s">
         <v>242</v>
       </c>
@@ -43753,7 +43752,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="641" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:18" ht="60" hidden="1">
       <c r="A641" s="22" t="s">
         <v>245</v>
       </c>
@@ -43809,7 +43808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="642" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:18" ht="60" hidden="1">
       <c r="A642" s="22" t="s">
         <v>248</v>
       </c>
@@ -43865,7 +43864,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="643" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:18" ht="60" hidden="1">
       <c r="A643" s="22" t="s">
         <v>250</v>
       </c>
@@ -43921,7 +43920,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="644" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:18" ht="60" hidden="1">
       <c r="A644" s="22" t="s">
         <v>253</v>
       </c>
@@ -43977,7 +43976,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="645" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:18" ht="60" hidden="1">
       <c r="A645" s="22" t="s">
         <v>254</v>
       </c>
@@ -44033,7 +44032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="646" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:18" ht="60" hidden="1">
       <c r="A646" s="22" t="s">
         <v>256</v>
       </c>
@@ -44089,7 +44088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="647" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:18" ht="60" hidden="1">
       <c r="A647" s="22" t="s">
         <v>258</v>
       </c>
@@ -44145,7 +44144,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="648" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:18" ht="60" hidden="1">
       <c r="A648" s="22" t="s">
         <v>260</v>
       </c>
@@ -44201,7 +44200,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="649" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:18" ht="60" hidden="1">
       <c r="A649" s="22" t="s">
         <v>264</v>
       </c>
@@ -44257,7 +44256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="650" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:18" ht="60" hidden="1">
       <c r="A650" s="22" t="s">
         <v>267</v>
       </c>
@@ -44313,7 +44312,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="651" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:18" ht="75" hidden="1">
       <c r="A651" s="22" t="s">
         <v>268</v>
       </c>
@@ -44369,7 +44368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="652" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:18" ht="60" hidden="1">
       <c r="A652" s="22" t="s">
         <v>271</v>
       </c>
@@ -44425,7 +44424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="653" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:18" ht="60" hidden="1">
       <c r="A653" s="22" t="s">
         <v>273</v>
       </c>
@@ -44481,7 +44480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="654" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:18" ht="60" hidden="1">
       <c r="A654" s="22" t="s">
         <v>276</v>
       </c>
@@ -44537,7 +44536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="655" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:18" ht="60" hidden="1">
       <c r="A655" s="22" t="s">
         <v>279</v>
       </c>
@@ -44593,7 +44592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="656" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:18" ht="60" hidden="1">
       <c r="A656" s="22" t="s">
         <v>282</v>
       </c>
@@ -44649,7 +44648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="657" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:18" ht="60" hidden="1">
       <c r="A657" s="22" t="s">
         <v>285</v>
       </c>
@@ -44705,7 +44704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="658" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:18" ht="60" hidden="1">
       <c r="A658" s="22" t="s">
         <v>287</v>
       </c>
@@ -44761,7 +44760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="659" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:18" ht="60" hidden="1">
       <c r="A659" s="22" t="s">
         <v>289</v>
       </c>
@@ -44817,7 +44816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="660" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:18" ht="60" hidden="1">
       <c r="A660" s="22" t="s">
         <v>292</v>
       </c>
@@ -44873,7 +44872,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="661" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:18" ht="105" hidden="1">
       <c r="A661" s="22" t="s">
         <v>294</v>
       </c>
@@ -44929,7 +44928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="662" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:18" ht="105" hidden="1">
       <c r="A662" s="22" t="s">
         <v>296</v>
       </c>
@@ -44985,7 +44984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="663" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:18" ht="105" hidden="1">
       <c r="A663" s="22" t="s">
         <v>299</v>
       </c>
@@ -45041,7 +45040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="664" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:18" ht="105" hidden="1">
       <c r="A664" s="22" t="s">
         <v>302</v>
       </c>
@@ -45097,7 +45096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="665" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:18" ht="105" hidden="1">
       <c r="A665" s="22" t="s">
         <v>305</v>
       </c>
@@ -45153,7 +45152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="666" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:18" ht="105" hidden="1">
       <c r="A666" s="22" t="s">
         <v>308</v>
       </c>
@@ -45246,7 +45245,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -45256,7 +45255,7 @@
     <col min="6" max="6" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="105.75" customHeight="1">
       <c r="B3" s="27" t="s">
         <v>1797</v>
       </c>
@@ -45266,7 +45265,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>1936</v>
       </c>
@@ -45287,7 +45286,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="22.5">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -45308,7 +45307,7 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -45329,7 +45328,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -45350,7 +45349,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -45371,7 +45370,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -45392,7 +45391,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -45413,7 +45412,7 @@
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -45434,7 +45433,7 @@
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -45455,7 +45454,7 @@
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="7">
         <v>9</v>
       </c>
@@ -45476,7 +45475,7 @@
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -45497,7 +45496,7 @@
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="7">
         <v>11</v>
       </c>
@@ -45518,7 +45517,7 @@
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -45539,7 +45538,7 @@
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="22.5">
       <c r="A17" s="7">
         <v>13</v>
       </c>
@@ -45560,7 +45559,7 @@
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="22.5">
       <c r="A18" s="7">
         <v>14</v>
       </c>
@@ -45581,7 +45580,7 @@
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="7">
         <v>15</v>
       </c>
@@ -45602,7 +45601,7 @@
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="7">
         <v>16</v>
       </c>
@@ -45623,7 +45622,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="22.5">
       <c r="A21" s="7">
         <v>17</v>
       </c>
@@ -45644,7 +45643,7 @@
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="7">
         <v>18</v>
       </c>
@@ -45665,7 +45664,7 @@
       </c>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="22.5">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -45686,7 +45685,7 @@
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="22.5">
       <c r="A24" s="7">
         <v>20</v>
       </c>
@@ -45707,7 +45706,7 @@
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="7">
         <v>21</v>
       </c>
@@ -45728,7 +45727,7 @@
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="22.5">
       <c r="A26" s="7">
         <v>22</v>
       </c>
@@ -45749,7 +45748,7 @@
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="22.5">
       <c r="A27" s="7">
         <v>23</v>
       </c>
@@ -45770,7 +45769,7 @@
       </c>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="7">
         <v>24</v>
       </c>
@@ -45791,7 +45790,7 @@
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="7">
         <v>25</v>
       </c>
@@ -45812,7 +45811,7 @@
       </c>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="22.5">
       <c r="A30" s="7">
         <v>26</v>
       </c>
@@ -45833,7 +45832,7 @@
       </c>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="22.5">
       <c r="A31" s="7">
         <v>27</v>
       </c>
@@ -45854,7 +45853,7 @@
       </c>
       <c r="G31" s="7"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5">
       <c r="B36" s="10" t="s">
         <v>1937</v>
       </c>
@@ -45868,7 +45867,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5">
       <c r="B37" s="5" t="s">
         <v>1938</v>
       </c>
@@ -45882,7 +45881,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5">
       <c r="B38" s="5" t="s">
         <v>1941</v>
       </c>
@@ -45896,7 +45895,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" ht="30">
       <c r="B39" s="5" t="s">
         <v>1943</v>
       </c>
@@ -45910,7 +45909,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5">
       <c r="B40" s="5" t="s">
         <v>1494</v>
       </c>
@@ -45924,7 +45923,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5">
       <c r="B41" s="5" t="s">
         <v>809</v>
       </c>
@@ -45938,7 +45937,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5">
       <c r="B42" s="5" t="s">
         <v>1946</v>
       </c>
@@ -45952,7 +45951,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5">
       <c r="B43" s="5" t="s">
         <v>1947</v>
       </c>
@@ -45966,7 +45965,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5">
       <c r="B44" s="5" t="s">
         <v>662</v>
       </c>
@@ -45980,7 +45979,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5">
       <c r="B45" s="5" t="s">
         <v>1948</v>
       </c>
@@ -45994,7 +45993,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5">
       <c r="B46" s="5" t="s">
         <v>1949</v>
       </c>
@@ -46008,7 +46007,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5">
       <c r="B47" s="5" t="s">
         <v>1834</v>
       </c>
@@ -46034,13 +46033,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="103.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
         <v>1952</v>
       </c>
@@ -46048,7 +46047,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>1956</v>
       </c>
@@ -46056,7 +46055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>1954</v>
       </c>
@@ -46064,7 +46063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>1953</v>
       </c>
@@ -46072,7 +46071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>1955</v>
       </c>
@@ -46080,7 +46079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>1957</v>
       </c>
@@ -46088,7 +46087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>1958</v>
       </c>
@@ -46096,7 +46095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="30">
       <c r="A8" s="4" t="s">
         <v>1959</v>
       </c>
@@ -46104,7 +46103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>1960</v>
       </c>
@@ -46112,7 +46111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="30">
       <c r="A10" t="s">
         <v>1961</v>
       </c>
@@ -46120,7 +46119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="30">
       <c r="A11" t="s">
         <v>1962</v>
       </c>
@@ -46128,7 +46127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="45">
       <c r="A12" t="s">
         <v>1963</v>
       </c>
@@ -46136,7 +46135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30">
       <c r="A13" t="s">
         <v>1964</v>
       </c>
@@ -46144,7 +46143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>1965</v>
       </c>
@@ -46152,7 +46151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="30">
       <c r="A15" t="s">
         <v>1966</v>
       </c>
@@ -46160,7 +46159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="30">
       <c r="A16" t="s">
         <v>1967</v>
       </c>
@@ -46168,37 +46167,37 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2">
       <c r="B17" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2">
       <c r="B21" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" s="2">
         <v>-1</v>
       </c>

--- a/docs/Airmius_Use_Cases_Testmatrix_testfreundlich org.xlsx
+++ b/docs/Airmius_Use_Cases_Testmatrix_testfreundlich org.xlsx
@@ -8114,7 +8114,7 @@
       </c>
       <c r="C2" s="18">
         <f>COUNTIF(B5:B800,"&lt;0")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="C3" s="18">
         <f>COUNTIF(B5:B800,"&gt;0")</f>
-        <v>441</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="C4" s="18">
         <f>COUNTIF(B5:B800,"=0")</f>
-        <v>193</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22" t="s">
         <v>704</v>
       </c>
@@ -13961,7 +13961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
         <v>870</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="22" t="s">
         <v>872</v>
       </c>
@@ -15809,7 +15809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="22" t="s">
         <v>977</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="22" t="s">
         <v>980</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="22" t="s">
         <v>1089</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="22" t="s">
         <v>1092</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="22" t="s">
         <v>1099</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="22" t="s">
         <v>1102</v>
       </c>
@@ -18329,7 +18329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="22" t="s">
         <v>1105</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="22" t="s">
         <v>1139</v>
       </c>
@@ -22193,7 +22193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="22" t="s">
         <v>1313</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="22" t="s">
         <v>1344</v>
       </c>
@@ -23481,7 +23481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="22" t="s">
         <v>1365</v>
       </c>
@@ -23537,7 +23537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="22" t="s">
         <v>1367</v>
       </c>
@@ -23593,7 +23593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="22" t="s">
         <v>1369</v>
       </c>
@@ -23649,7 +23649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="22" t="s">
         <v>1372</v>
       </c>
@@ -23705,12 +23705,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="22" t="s">
         <v>1375</v>
       </c>
       <c r="B283" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C283" s="18" t="s">
         <v>1376</v>
@@ -23873,12 +23873,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="22" t="s">
         <v>1384</v>
       </c>
       <c r="B286" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C286" s="18" t="s">
         <v>1385</v>
@@ -23985,12 +23985,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="22" t="s">
         <v>1390</v>
       </c>
       <c r="B288" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C288" s="18" t="s">
         <v>1391</v>
@@ -24097,12 +24097,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="22" t="s">
         <v>1399</v>
       </c>
       <c r="B290" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C290" s="18" t="s">
         <v>1400</v>
@@ -24153,12 +24153,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="22" t="s">
         <v>1402</v>
       </c>
       <c r="B291" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C291" s="18" t="s">
         <v>1403</v>
@@ -24377,12 +24377,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="22" t="s">
         <v>1416</v>
       </c>
       <c r="B295" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C295" s="18" t="s">
         <v>1417</v>
@@ -24433,12 +24433,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="22" t="s">
         <v>1419</v>
       </c>
       <c r="B296" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C296" s="18" t="s">
         <v>1420</v>
@@ -24489,12 +24489,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="22" t="s">
         <v>1422</v>
       </c>
       <c r="B297" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C297" s="18" t="s">
         <v>1423</v>
@@ -24545,12 +24545,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="22" t="s">
         <v>1424</v>
       </c>
       <c r="B298" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C298" s="18" t="s">
         <v>1425</v>
@@ -24601,12 +24601,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="22" t="s">
         <v>1426</v>
       </c>
       <c r="B299" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299" s="18" t="s">
         <v>1427</v>
@@ -24657,12 +24657,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="22" t="s">
         <v>1428</v>
       </c>
       <c r="B300" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C300" s="18" t="s">
         <v>1429</v>
@@ -24713,12 +24713,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="22" t="s">
         <v>1431</v>
       </c>
       <c r="B301" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C301" s="18" t="s">
         <v>1432</v>
@@ -24769,12 +24769,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="22" t="s">
         <v>1434</v>
       </c>
       <c r="B302" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C302" s="18" t="s">
         <v>1436</v>
@@ -24825,12 +24825,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="22" t="s">
         <v>1437</v>
       </c>
       <c r="B303" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C303" s="18" t="s">
         <v>1438</v>
@@ -26057,12 +26057,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="22" t="s">
         <v>1484</v>
       </c>
       <c r="B325" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C325" s="18" t="s">
         <v>1485</v>
@@ -26225,12 +26225,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="22" t="s">
         <v>1495</v>
       </c>
       <c r="B328" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C328" s="18" t="s">
         <v>1438</v>
@@ -26729,12 +26729,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="22" t="s">
         <v>1512</v>
       </c>
       <c r="B337" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C337" s="18" t="s">
         <v>1513</v>
@@ -26841,12 +26841,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="22" t="s">
         <v>1518</v>
       </c>
       <c r="B339" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C339" s="18" t="s">
         <v>1519</v>
@@ -27009,12 +27009,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="22" t="s">
         <v>1527</v>
       </c>
       <c r="B342" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C342" s="18" t="s">
         <v>1528</v>
@@ -27121,12 +27121,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="22" t="s">
         <v>1533</v>
       </c>
       <c r="B344" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C344" s="18" t="s">
         <v>1534</v>
@@ -27177,12 +27177,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="22" t="s">
         <v>1536</v>
       </c>
       <c r="B345" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C345" s="18" t="s">
         <v>1537</v>
@@ -27233,12 +27233,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="22" t="s">
         <v>1539</v>
       </c>
       <c r="B346" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C346" s="18" t="s">
         <v>1540</v>
@@ -27289,12 +27289,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="22" t="s">
         <v>1542</v>
       </c>
       <c r="B347" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C347" s="18" t="s">
         <v>1543</v>
@@ -27345,12 +27345,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="22" t="s">
         <v>1545</v>
       </c>
       <c r="B348" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C348" s="18" t="s">
         <v>1546</v>
@@ -27569,12 +27569,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="22" t="s">
         <v>1557</v>
       </c>
       <c r="B352" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C352" s="18" t="s">
         <v>1558</v>
@@ -27625,12 +27625,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="22" t="s">
         <v>1560</v>
       </c>
       <c r="B353" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C353" s="18" t="s">
         <v>1561</v>
@@ -27681,12 +27681,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="22" t="s">
         <v>1563</v>
       </c>
       <c r="B354" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C354" s="18" t="s">
         <v>1564</v>
@@ -28521,12 +28521,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="22" t="s">
         <v>1605</v>
       </c>
       <c r="B369" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C369" s="18" t="s">
         <v>1606</v>
@@ -28577,12 +28577,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="22" t="s">
         <v>1607</v>
       </c>
       <c r="B370" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C370" s="18" t="s">
         <v>1608</v>
@@ -28633,12 +28633,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="22" t="s">
         <v>1609</v>
       </c>
       <c r="B371" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C371" s="18" t="s">
         <v>1610</v>
@@ -28689,12 +28689,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="22" t="s">
         <v>1611</v>
       </c>
       <c r="B372" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C372" s="18" t="s">
         <v>1612</v>
@@ -28745,12 +28745,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="22" t="s">
         <v>1613</v>
       </c>
       <c r="B373" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C373" s="18" t="s">
         <v>1281</v>
@@ -28801,12 +28801,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="22" t="s">
         <v>1614</v>
       </c>
       <c r="B374" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C374" s="18" t="s">
         <v>1615</v>
@@ -29025,12 +29025,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="22" t="s">
         <v>1626</v>
       </c>
       <c r="B378" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C378" s="18" t="s">
         <v>1627</v>
@@ -29081,12 +29081,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="22" t="s">
         <v>1629</v>
       </c>
       <c r="B379" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C379" s="18" t="s">
         <v>1630</v>
@@ -29137,12 +29137,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="22" t="s">
         <v>1632</v>
       </c>
       <c r="B380" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C380" s="18" t="s">
         <v>1633</v>
@@ -29193,12 +29193,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="22" t="s">
         <v>1635</v>
       </c>
       <c r="B381" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C381" s="18" t="s">
         <v>1636</v>
@@ -29641,12 +29641,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="22" t="s">
         <v>1660</v>
       </c>
       <c r="B389" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C389" s="18" t="s">
         <v>1661</v>
@@ -29697,12 +29697,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="22" t="s">
         <v>1663</v>
       </c>
       <c r="B390" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C390" s="18" t="s">
         <v>1664</v>
@@ -29753,12 +29753,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="22" t="s">
         <v>1666</v>
       </c>
       <c r="B391" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C391" s="18" t="s">
         <v>1667</v>
@@ -29809,12 +29809,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="22" t="s">
         <v>1669</v>
       </c>
       <c r="B392" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C392" s="18" t="s">
         <v>1670</v>
@@ -29865,12 +29865,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="22" t="s">
         <v>1672</v>
       </c>
       <c r="B393" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C393" s="18" t="s">
         <v>1673</v>
@@ -30094,7 +30094,7 @@
         <v>1684</v>
       </c>
       <c r="B397" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C397" s="18" t="s">
         <v>1685</v>
@@ -30430,7 +30430,7 @@
         <v>1700</v>
       </c>
       <c r="B403" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C403" s="18" t="s">
         <v>1701</v>
@@ -31550,7 +31550,7 @@
         <v>1758</v>
       </c>
       <c r="B423" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C423" s="18" t="s">
         <v>1759</v>
@@ -31606,7 +31606,7 @@
         <v>1761</v>
       </c>
       <c r="B424" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C424" s="18" t="s">
         <v>1762</v>
@@ -31774,7 +31774,7 @@
         <v>1771</v>
       </c>
       <c r="B427" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C427" s="18" t="s">
         <v>1772</v>
@@ -31830,7 +31830,7 @@
         <v>1774</v>
       </c>
       <c r="B428" s="16">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="C428" s="18" t="s">
         <v>1775</v>
@@ -31998,7 +31998,7 @@
         <v>1783</v>
       </c>
       <c r="B431" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C431" s="18" t="s">
         <v>1784</v>
@@ -32054,7 +32054,7 @@
         <v>1786</v>
       </c>
       <c r="B432" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C432" s="18" t="s">
         <v>1787</v>

--- a/docs/Airmius_Use_Cases_Testmatrix_testfreundlich org.xlsx
+++ b/docs/Airmius_Use_Cases_Testmatrix_testfreundlich org.xlsx
@@ -7225,7 +7225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -8086,7 +8086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R666"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" customWidth="1"/>
@@ -8104,40 +8104,40 @@
     <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="A1" s="22"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18">
       <c r="A2" s="22"/>
       <c r="B2" s="7" t="s">
         <v>1970</v>
       </c>
       <c r="C2" s="18">
         <f>COUNTIF(B5:B800,"&lt;0")</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="22"/>
       <c r="B3" s="7" t="s">
         <v>1971</v>
       </c>
       <c r="C3" s="18">
         <f>COUNTIF(B5:B800,"&gt;0")</f>
-        <v>490</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="22"/>
       <c r="B4" s="7" t="s">
         <v>1972</v>
       </c>
       <c r="C4" s="18">
         <f>COUNTIF(B5:B800,"=0")</f>
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="20" t="s">
         <v>0</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
       <c r="A6" s="22" t="s">
         <v>82</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
       <c r="A7" s="22" t="s">
         <v>240</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
       <c r="A8" s="22" t="s">
         <v>263</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
       <c r="A9" s="22" t="s">
         <v>342</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
       <c r="A10" s="22" t="s">
         <v>99</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
       <c r="A11" s="22" t="s">
         <v>101</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="195" hidden="1">
       <c r="A12" s="22" t="s">
         <v>103</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="75" hidden="1">
       <c r="A13" s="22" t="s">
         <v>122</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="75" hidden="1">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="75" hidden="1">
       <c r="A15" s="22" t="s">
         <v>134</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="75" hidden="1">
       <c r="A16" s="22" t="s">
         <v>150</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="60" hidden="1">
       <c r="A17" s="22" t="s">
         <v>220</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="75" hidden="1">
       <c r="A18" s="22" t="s">
         <v>225</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="75" hidden="1">
       <c r="A19" s="22" t="s">
         <v>1969</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="60" hidden="1">
       <c r="A20" s="22" t="s">
         <v>414</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="60" hidden="1">
       <c r="A21" s="22" t="s">
         <v>417</v>
       </c>
@@ -9089,7 +9089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="60" hidden="1">
       <c r="A22" s="22" t="s">
         <v>420</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="90" hidden="1">
       <c r="A23" s="22" t="s">
         <v>430</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="90" hidden="1">
       <c r="A24" s="22" t="s">
         <v>439</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="90" hidden="1">
       <c r="A25" s="22" t="s">
         <v>442</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="90" hidden="1">
       <c r="A26" s="22" t="s">
         <v>445</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="90" hidden="1">
       <c r="A27" s="22" t="s">
         <v>448</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="60" hidden="1">
       <c r="A28" s="22" t="s">
         <v>457</v>
       </c>
@@ -9481,7 +9481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="60" hidden="1">
       <c r="A29" s="22" t="s">
         <v>460</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="60" hidden="1">
       <c r="A30" s="22" t="s">
         <v>463</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="60" hidden="1">
       <c r="A31" s="22" t="s">
         <v>466</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="60" hidden="1">
       <c r="A32" s="22" t="s">
         <v>494</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="75" hidden="1">
       <c r="A33" s="22" t="s">
         <v>500</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="75" hidden="1">
       <c r="A34" s="22" t="s">
         <v>503</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="60" hidden="1">
       <c r="A35" s="22" t="s">
         <v>514</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="60" hidden="1">
       <c r="A36" s="22" t="s">
         <v>563</v>
       </c>
@@ -9929,7 +9929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="60" hidden="1">
       <c r="A37" s="22" t="s">
         <v>565</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="60" hidden="1">
       <c r="A38" s="22" t="s">
         <v>574</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="75" hidden="1">
       <c r="A39" s="22" t="s">
         <v>577</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="75" hidden="1">
       <c r="A40" s="22" t="s">
         <v>580</v>
       </c>
@@ -10153,7 +10153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="75" hidden="1">
       <c r="A41" s="22" t="s">
         <v>583</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="75" hidden="1">
       <c r="A42" s="22" t="s">
         <v>586</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="60" hidden="1">
       <c r="A43" s="22" t="s">
         <v>589</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="60" hidden="1">
       <c r="A44" s="22" t="s">
         <v>591</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="60" hidden="1">
       <c r="A45" s="22" t="s">
         <v>595</v>
       </c>
@@ -10433,7 +10433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="60" hidden="1">
       <c r="A46" s="22" t="s">
         <v>598</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="60" hidden="1">
       <c r="A47" s="22" t="s">
         <v>601</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="26" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" s="26" customFormat="1" ht="60" hidden="1">
       <c r="A48" s="22" t="s">
         <v>604</v>
       </c>
@@ -10601,7 +10601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="60" hidden="1">
       <c r="A49" s="22" t="s">
         <v>606</v>
       </c>
@@ -10657,7 +10657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="60" hidden="1">
       <c r="A50" s="22" t="s">
         <v>608</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="60" hidden="1">
       <c r="A51" s="22" t="s">
         <v>612</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="60" hidden="1">
       <c r="A52" s="22" t="s">
         <v>614</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="60" hidden="1">
       <c r="A53" s="22" t="s">
         <v>616</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="60" hidden="1">
       <c r="A54" s="22" t="s">
         <v>618</v>
       </c>
@@ -10937,7 +10937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="345" hidden="1">
       <c r="A55" s="22" t="s">
         <v>684</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="135" hidden="1">
       <c r="A56" s="22" t="s">
         <v>687</v>
       </c>
@@ -11049,7 +11049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="135" hidden="1">
       <c r="A57" s="22" t="s">
         <v>689</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="135" hidden="1">
       <c r="A58" s="22" t="s">
         <v>692</v>
       </c>
@@ -11161,7 +11161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="135" hidden="1">
       <c r="A59" s="22" t="s">
         <v>700</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="135" hidden="1">
       <c r="A60" s="22" t="s">
         <v>703</v>
       </c>
@@ -11273,7 +11273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="135" hidden="1">
       <c r="A61" s="22" t="s">
         <v>704</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="60" hidden="1">
       <c r="A62" s="22" t="s">
         <v>706</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="75" hidden="1">
       <c r="A63" s="22" t="s">
         <v>711</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="75" hidden="1">
       <c r="A64" s="22" t="s">
         <v>714</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="60" hidden="1">
       <c r="A65" s="22" t="s">
         <v>716</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="60" hidden="1">
       <c r="A66" s="22" t="s">
         <v>719</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="60" hidden="1">
       <c r="A67" s="22" t="s">
         <v>722</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="60" hidden="1">
       <c r="A68" s="22" t="s">
         <v>725</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="75" hidden="1">
       <c r="A69" s="22" t="s">
         <v>728</v>
       </c>
@@ -11777,7 +11777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="150" hidden="1">
       <c r="A70" s="22" t="s">
         <v>744</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="150" hidden="1">
       <c r="A71" s="22" t="s">
         <v>748</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="150" hidden="1">
       <c r="A72" s="22" t="s">
         <v>751</v>
       </c>
@@ -11945,7 +11945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="150" hidden="1">
       <c r="A73" s="22" t="s">
         <v>754</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="150" hidden="1">
       <c r="A74" s="22" t="s">
         <v>757</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="150" hidden="1">
       <c r="A75" s="22" t="s">
         <v>760</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="150" hidden="1">
       <c r="A76" s="22" t="s">
         <v>763</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="150" hidden="1">
       <c r="A77" s="22" t="s">
         <v>765</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="150" hidden="1">
       <c r="A78" s="22" t="s">
         <v>768</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="150" hidden="1">
       <c r="A79" s="22" t="s">
         <v>771</v>
       </c>
@@ -12337,7 +12337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="150" hidden="1">
       <c r="A80" s="22" t="s">
         <v>774</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="60" hidden="1">
       <c r="A81" s="22" t="s">
         <v>777</v>
       </c>
@@ -12449,7 +12449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="60" hidden="1">
       <c r="A82" s="22" t="s">
         <v>785</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="60" hidden="1">
       <c r="A83" s="22" t="s">
         <v>787</v>
       </c>
@@ -12561,7 +12561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="60" hidden="1">
       <c r="A84" s="22" t="s">
         <v>788</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="60" hidden="1">
       <c r="A85" s="22" t="s">
         <v>790</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="60" hidden="1">
       <c r="A86" s="22" t="s">
         <v>791</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="60" hidden="1">
       <c r="A87" s="22" t="s">
         <v>794</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="60" hidden="1">
       <c r="A88" s="22" t="s">
         <v>797</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="60" hidden="1">
       <c r="A89" s="22" t="s">
         <v>798</v>
       </c>
@@ -12897,7 +12897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="60" hidden="1">
       <c r="A90" s="22" t="s">
         <v>799</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="60" hidden="1">
       <c r="A91" s="22" t="s">
         <v>801</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="60" hidden="1">
       <c r="A92" s="22" t="s">
         <v>804</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="135" hidden="1">
       <c r="A93" s="22" t="s">
         <v>807</v>
       </c>
@@ -13121,7 +13121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="135" hidden="1">
       <c r="A94" s="22" t="s">
         <v>809</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="135" hidden="1">
       <c r="A95" s="22" t="s">
         <v>811</v>
       </c>
@@ -13233,7 +13233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="135" hidden="1">
       <c r="A96" s="22" t="s">
         <v>813</v>
       </c>
@@ -13289,7 +13289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="135" hidden="1">
       <c r="A97" s="22" t="s">
         <v>815</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="135" hidden="1">
       <c r="A98" s="22" t="s">
         <v>818</v>
       </c>
@@ -13401,7 +13401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="135" hidden="1">
       <c r="A99" s="22" t="s">
         <v>820</v>
       </c>
@@ -13457,7 +13457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="409.5" hidden="1">
       <c r="A100" s="22" t="s">
         <v>831</v>
       </c>
@@ -13513,7 +13513,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="409.5" hidden="1">
       <c r="A101" s="22" t="s">
         <v>834</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="409.5" hidden="1">
       <c r="A102" s="22" t="s">
         <v>851</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="409.5" hidden="1">
       <c r="A103" s="22" t="s">
         <v>853</v>
       </c>
@@ -13681,7 +13681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="409.5" hidden="1">
       <c r="A104" s="22" t="s">
         <v>855</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="409.5" hidden="1">
       <c r="A105" s="22" t="s">
         <v>857</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="409.5" hidden="1">
       <c r="A106" s="22" t="s">
         <v>859</v>
       </c>
@@ -13849,7 +13849,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="409.5" hidden="1">
       <c r="A107" s="22" t="s">
         <v>865</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="409.5" hidden="1">
       <c r="A108" s="22" t="s">
         <v>867</v>
       </c>
@@ -13961,7 +13961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="409.5" hidden="1">
       <c r="A109" s="22" t="s">
         <v>870</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="409.5" hidden="1">
       <c r="A110" s="22" t="s">
         <v>872</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="409.5" hidden="1">
       <c r="A111" s="22" t="s">
         <v>878</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="409.5" hidden="1">
       <c r="A112" s="22" t="s">
         <v>880</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="60" hidden="1">
       <c r="A113" s="22" t="s">
         <v>883</v>
       </c>
@@ -14241,7 +14241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="60" hidden="1">
       <c r="A114" s="22" t="s">
         <v>889</v>
       </c>
@@ -14297,7 +14297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="60" hidden="1">
       <c r="A115" s="22" t="s">
         <v>892</v>
       </c>
@@ -14353,7 +14353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="60" hidden="1">
       <c r="A116" s="22" t="s">
         <v>893</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="60" hidden="1">
       <c r="A117" s="22" t="s">
         <v>895</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="60" hidden="1">
       <c r="A118" s="22" t="s">
         <v>900</v>
       </c>
@@ -14521,7 +14521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="75" hidden="1">
       <c r="A119" s="22" t="s">
         <v>908</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="60" hidden="1">
       <c r="A120" s="22" t="s">
         <v>911</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="75" hidden="1">
       <c r="A121" s="22" t="s">
         <v>914</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="75" hidden="1">
       <c r="A122" s="22" t="s">
         <v>917</v>
       </c>
@@ -14745,7 +14745,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="60" hidden="1">
       <c r="A123" s="22" t="s">
         <v>920</v>
       </c>
@@ -14801,7 +14801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="60" hidden="1">
       <c r="A124" s="22" t="s">
         <v>923</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="60" hidden="1">
       <c r="A125" s="22" t="s">
         <v>926</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="60" hidden="1">
       <c r="A126" s="22" t="s">
         <v>929</v>
       </c>
@@ -14969,7 +14969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="75" hidden="1">
       <c r="A127" s="22" t="s">
         <v>932</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="75" hidden="1">
       <c r="A128" s="22" t="s">
         <v>935</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="75" hidden="1">
       <c r="A129" s="22" t="s">
         <v>938</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="75" hidden="1">
       <c r="A130" s="22" t="s">
         <v>941</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="60" hidden="1">
       <c r="A131" s="22" t="s">
         <v>944</v>
       </c>
@@ -15249,7 +15249,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="60" hidden="1">
       <c r="A132" s="22" t="s">
         <v>947</v>
       </c>
@@ -15305,7 +15305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="60" hidden="1">
       <c r="A133" s="22" t="s">
         <v>949</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="60" hidden="1">
       <c r="A134" s="22" t="s">
         <v>952</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="60" hidden="1">
       <c r="A135" s="22" t="s">
         <v>954</v>
       </c>
@@ -15473,7 +15473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="60" hidden="1">
       <c r="A136" s="22" t="s">
         <v>956</v>
       </c>
@@ -15529,7 +15529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="60" hidden="1">
       <c r="A137" s="22" t="s">
         <v>958</v>
       </c>
@@ -15585,7 +15585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="60" hidden="1">
       <c r="A138" s="22" t="s">
         <v>961</v>
       </c>
@@ -15641,7 +15641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="60" hidden="1">
       <c r="A139" s="22" t="s">
         <v>963</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="60" hidden="1">
       <c r="A140" s="22" t="s">
         <v>966</v>
       </c>
@@ -15753,7 +15753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="60" hidden="1">
       <c r="A141" s="22" t="s">
         <v>971</v>
       </c>
@@ -15809,7 +15809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="60" hidden="1">
       <c r="A142" s="22" t="s">
         <v>977</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="60" hidden="1">
       <c r="A143" s="22" t="s">
         <v>980</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="60">
       <c r="A144" s="22" t="s">
         <v>983</v>
       </c>
@@ -15977,7 +15977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="60">
       <c r="A145" s="22" t="s">
         <v>986</v>
       </c>
@@ -16033,7 +16033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="60" hidden="1">
       <c r="A146" s="22" t="s">
         <v>989</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="60" hidden="1">
       <c r="A147" s="22" t="s">
         <v>992</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="60">
       <c r="A148" s="22" t="s">
         <v>995</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="60">
       <c r="A149" s="22" t="s">
         <v>998</v>
       </c>
@@ -16257,7 +16257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="60">
       <c r="A150" s="22" t="s">
         <v>1001</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="60" hidden="1">
       <c r="A151" s="22" t="s">
         <v>1004</v>
       </c>
@@ -16369,7 +16369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="60" hidden="1">
       <c r="A152" s="22" t="s">
         <v>1009</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="75" hidden="1">
       <c r="A153" s="22" t="s">
         <v>1011</v>
       </c>
@@ -16481,7 +16481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="60" hidden="1">
       <c r="A154" s="22" t="s">
         <v>1014</v>
       </c>
@@ -16537,7 +16537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="60" hidden="1">
       <c r="A155" s="22" t="s">
         <v>1017</v>
       </c>
@@ -16593,7 +16593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="60" hidden="1">
       <c r="A156" s="22" t="s">
         <v>1020</v>
       </c>
@@ -16649,7 +16649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="60" hidden="1">
       <c r="A157" s="22" t="s">
         <v>1023</v>
       </c>
@@ -16705,7 +16705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="60" hidden="1">
       <c r="A158" s="22" t="s">
         <v>1026</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="60" hidden="1">
       <c r="A159" s="22" t="s">
         <v>1029</v>
       </c>
@@ -16817,7 +16817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="60" hidden="1">
       <c r="A160" s="22" t="s">
         <v>1032</v>
       </c>
@@ -16873,7 +16873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="60" hidden="1">
       <c r="A161" s="22" t="s">
         <v>1035</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="60">
       <c r="A162" s="22" t="s">
         <v>1037</v>
       </c>
@@ -16985,12 +16985,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="60" hidden="1">
       <c r="A163" s="22" t="s">
         <v>1039</v>
       </c>
       <c r="B163" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" s="18" t="s">
         <v>1041</v>
@@ -17041,7 +17041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="60" hidden="1">
       <c r="A164" s="22" t="s">
         <v>1043</v>
       </c>
@@ -17097,7 +17097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="60" hidden="1">
       <c r="A165" s="22" t="s">
         <v>1046</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="60" hidden="1">
       <c r="A166" s="22" t="s">
         <v>1049</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="60" hidden="1">
       <c r="A167" s="22" t="s">
         <v>1052</v>
       </c>
@@ -17265,7 +17265,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="60" hidden="1">
       <c r="A168" s="22" t="s">
         <v>1055</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="60" hidden="1">
       <c r="A169" s="22" t="s">
         <v>1058</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="75" hidden="1">
       <c r="A170" s="22" t="s">
         <v>1061</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="60" hidden="1">
       <c r="A171" s="22" t="s">
         <v>1064</v>
       </c>
@@ -17489,7 +17489,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="60" hidden="1">
       <c r="A172" s="22" t="s">
         <v>1067</v>
       </c>
@@ -17545,7 +17545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="60" hidden="1">
       <c r="A173" s="22" t="s">
         <v>1070</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="60" hidden="1">
       <c r="A174" s="22" t="s">
         <v>1073</v>
       </c>
@@ -17657,7 +17657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="60">
       <c r="A175" s="22" t="s">
         <v>1075</v>
       </c>
@@ -17713,7 +17713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="60">
       <c r="A176" s="22" t="s">
         <v>1077</v>
       </c>
@@ -17769,12 +17769,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="60">
       <c r="A177" s="22" t="s">
         <v>1079</v>
       </c>
       <c r="B177" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" s="18" t="s">
         <v>1080</v>
@@ -17825,12 +17825,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="60">
       <c r="A178" s="22" t="s">
         <v>1081</v>
       </c>
       <c r="B178" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>1082</v>
@@ -17881,7 +17881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="60">
       <c r="A179" s="22" t="s">
         <v>1083</v>
       </c>
@@ -17937,7 +17937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="60">
       <c r="A180" s="22" t="s">
         <v>1086</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="60" hidden="1">
       <c r="A181" s="22" t="s">
         <v>1089</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="60" hidden="1">
       <c r="A182" s="22" t="s">
         <v>1092</v>
       </c>
@@ -18105,7 +18105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="60" hidden="1">
       <c r="A183" s="22" t="s">
         <v>1094</v>
       </c>
@@ -18161,7 +18161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="60" hidden="1">
       <c r="A184" s="22" t="s">
         <v>1097</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="60" hidden="1">
       <c r="A185" s="22" t="s">
         <v>1099</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="60" hidden="1">
       <c r="A186" s="22" t="s">
         <v>1102</v>
       </c>
@@ -18329,7 +18329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="75" hidden="1">
       <c r="A187" s="22" t="s">
         <v>1105</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="60" hidden="1">
       <c r="A188" s="22" t="s">
         <v>1108</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="60" hidden="1">
       <c r="A189" s="22" t="s">
         <v>1110</v>
       </c>
@@ -18497,7 +18497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="60" hidden="1">
       <c r="A190" s="22" t="s">
         <v>1112</v>
       </c>
@@ -18553,7 +18553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="60" hidden="1">
       <c r="A191" s="22" t="s">
         <v>1115</v>
       </c>
@@ -18609,12 +18609,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="60" hidden="1">
       <c r="A192" s="22" t="s">
         <v>1118</v>
       </c>
       <c r="B192" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" s="18" t="s">
         <v>1119</v>
@@ -18665,12 +18665,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="60" hidden="1">
       <c r="A193" s="22" t="s">
         <v>1121</v>
       </c>
       <c r="B193" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C193" s="18" t="s">
         <v>1122</v>
@@ -18721,7 +18721,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="60" hidden="1">
       <c r="A194" s="22" t="s">
         <v>1124</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="60" hidden="1">
       <c r="A195" s="22" t="s">
         <v>1126</v>
       </c>
@@ -18833,7 +18833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="90" hidden="1">
       <c r="A196" s="22" t="s">
         <v>1129</v>
       </c>
@@ -18889,7 +18889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="90">
       <c r="A197" s="22" t="s">
         <v>1132</v>
       </c>
@@ -18945,7 +18945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="75">
       <c r="A198" s="22" t="s">
         <v>1135</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="75" hidden="1">
       <c r="A199" s="22" t="s">
         <v>1139</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="75">
       <c r="A200" s="22" t="s">
         <v>1142</v>
       </c>
@@ -19113,7 +19113,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="75" hidden="1">
       <c r="A201" s="22" t="s">
         <v>1145</v>
       </c>
@@ -19169,7 +19169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="75" hidden="1">
       <c r="A202" s="22" t="s">
         <v>1148</v>
       </c>
@@ -19225,7 +19225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="75" hidden="1">
       <c r="A203" s="22" t="s">
         <v>1150</v>
       </c>
@@ -19281,7 +19281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="75" hidden="1">
       <c r="A204" s="22" t="s">
         <v>1153</v>
       </c>
@@ -19337,7 +19337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="75">
       <c r="A205" s="22" t="s">
         <v>1156</v>
       </c>
@@ -19393,7 +19393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="75" hidden="1">
       <c r="A206" s="22" t="s">
         <v>1159</v>
       </c>
@@ -19449,7 +19449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="75" hidden="1">
       <c r="A207" s="22" t="s">
         <v>1162</v>
       </c>
@@ -19505,7 +19505,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="75">
       <c r="A208" s="22" t="s">
         <v>1165</v>
       </c>
@@ -19561,7 +19561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="75" hidden="1">
       <c r="A209" s="22" t="s">
         <v>1168</v>
       </c>
@@ -19617,7 +19617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="60" hidden="1">
       <c r="A210" s="22" t="s">
         <v>1171</v>
       </c>
@@ -19673,7 +19673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="60">
       <c r="A211" s="22" t="s">
         <v>1175</v>
       </c>
@@ -19729,7 +19729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="60" hidden="1">
       <c r="A212" s="22" t="s">
         <v>1178</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="60" hidden="1">
       <c r="A213" s="22" t="s">
         <v>1181</v>
       </c>
@@ -19841,7 +19841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="60">
       <c r="A214" s="22" t="s">
         <v>1184</v>
       </c>
@@ -19897,7 +19897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="60">
       <c r="A215" s="22" t="s">
         <v>1187</v>
       </c>
@@ -19953,7 +19953,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="60">
       <c r="A216" s="22" t="s">
         <v>1190</v>
       </c>
@@ -20009,7 +20009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ht="60">
       <c r="A217" s="22" t="s">
         <v>1193</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ht="60">
       <c r="A218" s="22" t="s">
         <v>1196</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="60">
       <c r="A219" s="22" t="s">
         <v>1199</v>
       </c>
@@ -20177,7 +20177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="60">
       <c r="A220" s="22" t="s">
         <v>1202</v>
       </c>
@@ -20233,7 +20233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="60">
       <c r="A221" s="22" t="s">
         <v>1205</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="60">
       <c r="A222" s="22" t="s">
         <v>1208</v>
       </c>
@@ -20345,7 +20345,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ht="195">
       <c r="A223" s="22" t="s">
         <v>1211</v>
       </c>
@@ -20401,7 +20401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ht="195">
       <c r="A224" s="22" t="s">
         <v>1214</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="195">
       <c r="A225" s="22" t="s">
         <v>1217</v>
       </c>
@@ -20513,7 +20513,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="75" hidden="1">
       <c r="A226" s="22" t="s">
         <v>1219</v>
       </c>
@@ -20569,7 +20569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="75" hidden="1">
       <c r="A227" s="22" t="s">
         <v>1223</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="75" hidden="1">
       <c r="A228" s="22" t="s">
         <v>1226</v>
       </c>
@@ -20681,7 +20681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" ht="75" hidden="1">
       <c r="A229" s="22" t="s">
         <v>1229</v>
       </c>
@@ -20737,7 +20737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="75" hidden="1">
       <c r="A230" s="22" t="s">
         <v>1232</v>
       </c>
@@ -20793,7 +20793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="75" hidden="1">
       <c r="A231" s="22" t="s">
         <v>1235</v>
       </c>
@@ -20849,7 +20849,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="75" hidden="1">
       <c r="A232" s="22" t="s">
         <v>1238</v>
       </c>
@@ -20905,7 +20905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="75" hidden="1">
       <c r="A233" s="22" t="s">
         <v>1241</v>
       </c>
@@ -20961,7 +20961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="75" hidden="1">
       <c r="A234" s="22" t="s">
         <v>1244</v>
       </c>
@@ -21017,7 +21017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ht="75" hidden="1">
       <c r="A235" s="22" t="s">
         <v>1247</v>
       </c>
@@ -21073,7 +21073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="75" hidden="1">
       <c r="A236" s="22" t="s">
         <v>1250</v>
       </c>
@@ -21129,7 +21129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ht="60">
       <c r="A237" s="22" t="s">
         <v>1253</v>
       </c>
@@ -21185,7 +21185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="60">
       <c r="A238" s="22" t="s">
         <v>1256</v>
       </c>
@@ -21241,7 +21241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ht="345">
       <c r="A239" s="22" t="s">
         <v>1258</v>
       </c>
@@ -21297,7 +21297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="345">
       <c r="A240" s="22" t="s">
         <v>1261</v>
       </c>
@@ -21353,7 +21353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="345">
       <c r="A241" s="22" t="s">
         <v>1264</v>
       </c>
@@ -21409,7 +21409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="75" hidden="1">
       <c r="A242" s="22" t="s">
         <v>1267</v>
       </c>
@@ -21465,7 +21465,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="60">
       <c r="A243" s="22" t="s">
         <v>1271</v>
       </c>
@@ -21521,7 +21521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ht="60">
       <c r="A244" s="22" t="s">
         <v>1274</v>
       </c>
@@ -21577,7 +21577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" ht="60">
       <c r="A245" s="22" t="s">
         <v>1277</v>
       </c>
@@ -21633,7 +21633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" ht="60">
       <c r="A246" s="22" t="s">
         <v>1280</v>
       </c>
@@ -21689,7 +21689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" ht="75">
       <c r="A247" s="22" t="s">
         <v>1283</v>
       </c>
@@ -21745,7 +21745,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" ht="75" hidden="1">
       <c r="A248" s="22" t="s">
         <v>1286</v>
       </c>
@@ -21801,7 +21801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" ht="60">
       <c r="A249" s="22" t="s">
         <v>1291</v>
       </c>
@@ -21857,7 +21857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" ht="60" hidden="1">
       <c r="A250" s="22" t="s">
         <v>1295</v>
       </c>
@@ -21913,7 +21913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" ht="60" hidden="1">
       <c r="A251" s="22" t="s">
         <v>1298</v>
       </c>
@@ -21969,7 +21969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ht="60">
       <c r="A252" s="22" t="s">
         <v>1301</v>
       </c>
@@ -22025,7 +22025,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" ht="60">
       <c r="A253" s="22" t="s">
         <v>1304</v>
       </c>
@@ -22081,7 +22081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" ht="60">
       <c r="A254" s="22" t="s">
         <v>1307</v>
       </c>
@@ -22137,12 +22137,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" ht="60">
       <c r="A255" s="22" t="s">
         <v>1310</v>
       </c>
       <c r="B255" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>1311</v>
@@ -22193,7 +22193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ht="60" hidden="1">
       <c r="A256" s="22" t="s">
         <v>1313</v>
       </c>
@@ -22249,7 +22249,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" ht="60">
       <c r="A257" s="22" t="s">
         <v>1316</v>
       </c>
@@ -22305,7 +22305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" ht="60">
       <c r="A258" s="22" t="s">
         <v>1319</v>
       </c>
@@ -22361,7 +22361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" ht="60">
       <c r="A259" s="22" t="s">
         <v>1321</v>
       </c>
@@ -22417,7 +22417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" ht="60">
       <c r="A260" s="22" t="s">
         <v>1323</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" ht="60">
       <c r="A261" s="22" t="s">
         <v>1325</v>
       </c>
@@ -22529,7 +22529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" ht="60">
       <c r="A262" s="22" t="s">
         <v>1327</v>
       </c>
@@ -22585,7 +22585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" ht="60">
       <c r="A263" s="22" t="s">
         <v>1330</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" ht="60">
       <c r="A264" s="22" t="s">
         <v>1332</v>
       </c>
@@ -22697,7 +22697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" ht="60">
       <c r="A265" s="22" t="s">
         <v>1334</v>
       </c>
@@ -22753,7 +22753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" ht="60">
       <c r="A266" s="22" t="s">
         <v>1336</v>
       </c>
@@ -22809,7 +22809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" ht="60">
       <c r="A267" s="22" t="s">
         <v>1339</v>
       </c>
@@ -22865,7 +22865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" ht="60">
       <c r="A268" s="22" t="s">
         <v>1341</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ht="60" hidden="1">
       <c r="A269" s="22" t="s">
         <v>1344</v>
       </c>
@@ -22977,7 +22977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" ht="409.5">
       <c r="A270" s="22" t="s">
         <v>1347</v>
       </c>
@@ -23033,7 +23033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" ht="409.5">
       <c r="A271" s="22" t="s">
         <v>1349</v>
       </c>
@@ -23089,7 +23089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" ht="409.5">
       <c r="A272" s="22" t="s">
         <v>1351</v>
       </c>
@@ -23145,7 +23145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" ht="409.5">
       <c r="A273" s="22" t="s">
         <v>1353</v>
       </c>
@@ -23201,7 +23201,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" ht="409.5">
       <c r="A274" s="22" t="s">
         <v>1355</v>
       </c>
@@ -23257,7 +23257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" ht="409.5">
       <c r="A275" s="22" t="s">
         <v>1357</v>
       </c>
@@ -23313,7 +23313,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" ht="409.5">
       <c r="A276" s="22" t="s">
         <v>1358</v>
       </c>
@@ -23369,7 +23369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" ht="409.5">
       <c r="A277" s="22" t="s">
         <v>1361</v>
       </c>
@@ -23425,7 +23425,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" ht="409.5">
       <c r="A278" s="22" t="s">
         <v>1363</v>
       </c>
@@ -23481,7 +23481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ht="409.5" hidden="1">
       <c r="A279" s="22" t="s">
         <v>1365</v>
       </c>
@@ -23537,7 +23537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ht="409.5" hidden="1">
       <c r="A280" s="22" t="s">
         <v>1367</v>
       </c>
@@ -23593,7 +23593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" ht="409.5" hidden="1">
       <c r="A281" s="22" t="s">
         <v>1369</v>
       </c>
@@ -23649,7 +23649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ht="409.5" hidden="1">
       <c r="A282" s="22" t="s">
         <v>1372</v>
       </c>
@@ -23705,7 +23705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ht="409.5" hidden="1">
       <c r="A283" s="22" t="s">
         <v>1375</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" ht="409.5">
       <c r="A284" s="22" t="s">
         <v>1378</v>
       </c>
@@ -23817,12 +23817,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" ht="409.5" hidden="1">
       <c r="A285" s="22" t="s">
         <v>1381</v>
       </c>
       <c r="B285" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C285" s="18" t="s">
         <v>1382</v>
@@ -23873,7 +23873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ht="409.5" hidden="1">
       <c r="A286" s="22" t="s">
         <v>1384</v>
       </c>
@@ -23929,12 +23929,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" ht="75" hidden="1">
       <c r="A287" s="22" t="s">
         <v>1387</v>
       </c>
       <c r="B287" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C287" s="18" t="s">
         <v>1388</v>
@@ -23985,7 +23985,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ht="330" hidden="1">
       <c r="A288" s="22" t="s">
         <v>1390</v>
       </c>
@@ -24041,12 +24041,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ht="75" hidden="1">
       <c r="A289" s="22" t="s">
         <v>1392</v>
       </c>
       <c r="B289" s="16">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="C289" s="18" t="s">
         <v>1395</v>
@@ -24097,7 +24097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ht="60" hidden="1">
       <c r="A290" s="22" t="s">
         <v>1399</v>
       </c>
@@ -24153,7 +24153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ht="75" hidden="1">
       <c r="A291" s="22" t="s">
         <v>1402</v>
       </c>
@@ -24209,12 +24209,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" ht="75" hidden="1">
       <c r="A292" s="22" t="s">
         <v>1405</v>
       </c>
       <c r="B292" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C292" s="18" t="s">
         <v>1406</v>
@@ -24265,12 +24265,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" ht="75" hidden="1">
       <c r="A293" s="22" t="s">
         <v>1408</v>
       </c>
       <c r="B293" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C293" s="18" t="s">
         <v>1409</v>
@@ -24321,12 +24321,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" ht="60" hidden="1">
       <c r="A294" s="22" t="s">
         <v>1411</v>
       </c>
       <c r="B294" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C294" s="18" t="s">
         <v>1414</v>
@@ -24377,7 +24377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ht="60" hidden="1">
       <c r="A295" s="22" t="s">
         <v>1416</v>
       </c>
@@ -24433,7 +24433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ht="60" hidden="1">
       <c r="A296" s="22" t="s">
         <v>1419</v>
       </c>
@@ -24489,7 +24489,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ht="60" hidden="1">
       <c r="A297" s="22" t="s">
         <v>1422</v>
       </c>
@@ -24545,7 +24545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ht="60" hidden="1">
       <c r="A298" s="22" t="s">
         <v>1424</v>
       </c>
@@ -24601,7 +24601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ht="60" hidden="1">
       <c r="A299" s="22" t="s">
         <v>1426</v>
       </c>
@@ -24657,7 +24657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ht="75" hidden="1">
       <c r="A300" s="22" t="s">
         <v>1428</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ht="60" hidden="1">
       <c r="A301" s="22" t="s">
         <v>1431</v>
       </c>
@@ -24769,7 +24769,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ht="60" hidden="1">
       <c r="A302" s="22" t="s">
         <v>1434</v>
       </c>
@@ -24825,7 +24825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ht="60" hidden="1">
       <c r="A303" s="22" t="s">
         <v>1437</v>
       </c>
@@ -24881,7 +24881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" ht="60" hidden="1">
       <c r="A304" s="22" t="s">
         <v>1439</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" ht="60" hidden="1">
       <c r="A305" s="22" t="s">
         <v>1441</v>
       </c>
@@ -24993,7 +24993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" ht="60" hidden="1">
       <c r="A306" s="22" t="s">
         <v>1443</v>
       </c>
@@ -25049,7 +25049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" ht="60" hidden="1">
       <c r="A307" s="22" t="s">
         <v>1445</v>
       </c>
@@ -25105,7 +25105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" ht="60" hidden="1">
       <c r="A308" s="22" t="s">
         <v>1447</v>
       </c>
@@ -25161,7 +25161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" ht="60" hidden="1">
       <c r="A309" s="22" t="s">
         <v>1449</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" ht="60" hidden="1">
       <c r="A310" s="22" t="s">
         <v>1451</v>
       </c>
@@ -25273,7 +25273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" ht="60" hidden="1">
       <c r="A311" s="22" t="s">
         <v>1453</v>
       </c>
@@ -25329,7 +25329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" ht="90" hidden="1">
       <c r="A312" s="22" t="s">
         <v>1455</v>
       </c>
@@ -25385,7 +25385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" ht="60" hidden="1">
       <c r="A313" s="22" t="s">
         <v>1458</v>
       </c>
@@ -25441,7 +25441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" ht="60">
       <c r="A314" s="22" t="s">
         <v>1461</v>
       </c>
@@ -25497,7 +25497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ht="60">
       <c r="A315" s="22" t="s">
         <v>1463</v>
       </c>
@@ -25553,7 +25553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" ht="60">
       <c r="A316" s="22" t="s">
         <v>1465</v>
       </c>
@@ -25609,7 +25609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ht="60">
       <c r="A317" s="22" t="s">
         <v>1467</v>
       </c>
@@ -25665,7 +25665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" ht="60">
       <c r="A318" s="22" t="s">
         <v>1469</v>
       </c>
@@ -25721,7 +25721,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" ht="60" hidden="1">
       <c r="A319" s="22" t="s">
         <v>1471</v>
       </c>
@@ -25777,7 +25777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" ht="60" hidden="1">
       <c r="A320" s="22" t="s">
         <v>1473</v>
       </c>
@@ -25833,7 +25833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ht="60" hidden="1">
       <c r="A321" s="22" t="s">
         <v>1475</v>
       </c>
@@ -25889,7 +25889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" ht="60" hidden="1">
       <c r="A322" s="22" t="s">
         <v>1477</v>
       </c>
@@ -25945,7 +25945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" ht="60" hidden="1">
       <c r="A323" s="22" t="s">
         <v>1479</v>
       </c>
@@ -26001,7 +26001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" ht="60">
       <c r="A324" s="22" t="s">
         <v>1482</v>
       </c>
@@ -26057,7 +26057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ht="60" hidden="1">
       <c r="A325" s="22" t="s">
         <v>1484</v>
       </c>
@@ -26113,7 +26113,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" ht="210" hidden="1">
       <c r="A326" s="22" t="s">
         <v>1487</v>
       </c>
@@ -26169,7 +26169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" ht="210" hidden="1">
       <c r="A327" s="22" t="s">
         <v>1492</v>
       </c>
@@ -26225,7 +26225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ht="210" hidden="1">
       <c r="A328" s="22" t="s">
         <v>1495</v>
       </c>
@@ -26281,7 +26281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" ht="210" hidden="1">
       <c r="A329" s="22" t="s">
         <v>1496</v>
       </c>
@@ -26337,7 +26337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" ht="210" hidden="1">
       <c r="A330" s="22" t="s">
         <v>1497</v>
       </c>
@@ -26393,7 +26393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" ht="210" hidden="1">
       <c r="A331" s="22" t="s">
         <v>1498</v>
       </c>
@@ -26449,7 +26449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" ht="210" hidden="1">
       <c r="A332" s="22" t="s">
         <v>1501</v>
       </c>
@@ -26505,7 +26505,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" ht="210" hidden="1">
       <c r="A333" s="22" t="s">
         <v>1503</v>
       </c>
@@ -26561,7 +26561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="210" hidden="1">
       <c r="A334" s="22" t="s">
         <v>1505</v>
       </c>
@@ -26617,7 +26617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="210" hidden="1">
       <c r="A335" s="22" t="s">
         <v>1507</v>
       </c>
@@ -26673,7 +26673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" ht="210" hidden="1">
       <c r="A336" s="22" t="s">
         <v>1509</v>
       </c>
@@ -26729,7 +26729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ht="210" hidden="1">
       <c r="A337" s="22" t="s">
         <v>1512</v>
       </c>
@@ -26785,12 +26785,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" ht="210" hidden="1">
       <c r="A338" s="22" t="s">
         <v>1515</v>
       </c>
       <c r="B338" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C338" s="18" t="s">
         <v>1516</v>
@@ -26841,7 +26841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ht="210" hidden="1">
       <c r="A339" s="22" t="s">
         <v>1518</v>
       </c>
@@ -26897,7 +26897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" ht="210">
       <c r="A340" s="22" t="s">
         <v>1521</v>
       </c>
@@ -26953,12 +26953,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" ht="210" hidden="1">
       <c r="A341" s="22" t="s">
         <v>1524</v>
       </c>
       <c r="B341" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C341" s="18" t="s">
         <v>1525</v>
@@ -27009,7 +27009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ht="210" hidden="1">
       <c r="A342" s="22" t="s">
         <v>1527</v>
       </c>
@@ -27065,7 +27065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" ht="210">
       <c r="A343" s="22" t="s">
         <v>1530</v>
       </c>
@@ -27121,7 +27121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ht="210" hidden="1">
       <c r="A344" s="22" t="s">
         <v>1533</v>
       </c>
@@ -27177,7 +27177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="210" hidden="1">
       <c r="A345" s="22" t="s">
         <v>1536</v>
       </c>
@@ -27233,7 +27233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ht="210" hidden="1">
       <c r="A346" s="22" t="s">
         <v>1539</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ht="210" hidden="1">
       <c r="A347" s="22" t="s">
         <v>1542</v>
       </c>
@@ -27345,7 +27345,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ht="210" hidden="1">
       <c r="A348" s="22" t="s">
         <v>1545</v>
       </c>
@@ -27401,7 +27401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" ht="210">
       <c r="A349" s="22" t="s">
         <v>1548</v>
       </c>
@@ -27457,7 +27457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" ht="210">
       <c r="A350" s="22" t="s">
         <v>1551</v>
       </c>
@@ -27513,7 +27513,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" ht="210">
       <c r="A351" s="22" t="s">
         <v>1554</v>
       </c>
@@ -27569,7 +27569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ht="210" hidden="1">
       <c r="A352" s="22" t="s">
         <v>1557</v>
       </c>
@@ -27625,7 +27625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="210" hidden="1">
       <c r="A353" s="22" t="s">
         <v>1560</v>
       </c>
@@ -27681,7 +27681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="210" hidden="1">
       <c r="A354" s="22" t="s">
         <v>1563</v>
       </c>
@@ -27737,7 +27737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="210" hidden="1">
       <c r="A355" s="22" t="s">
         <v>1566</v>
       </c>
@@ -27793,7 +27793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="210" hidden="1">
       <c r="A356" s="22" t="s">
         <v>1569</v>
       </c>
@@ -27849,7 +27849,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="210" hidden="1">
       <c r="A357" s="22" t="s">
         <v>1572</v>
       </c>
@@ -27905,7 +27905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="210">
       <c r="A358" s="22" t="s">
         <v>1575</v>
       </c>
@@ -27961,7 +27961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="210">
       <c r="A359" s="22" t="s">
         <v>1578</v>
       </c>
@@ -28017,7 +28017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="210">
       <c r="A360" s="22" t="s">
         <v>1581</v>
       </c>
@@ -28073,7 +28073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="210">
       <c r="A361" s="22" t="s">
         <v>1584</v>
       </c>
@@ -28129,7 +28129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="210">
       <c r="A362" s="22" t="s">
         <v>1587</v>
       </c>
@@ -28185,7 +28185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="210">
       <c r="A363" s="22" t="s">
         <v>1589</v>
       </c>
@@ -28241,7 +28241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" ht="210">
       <c r="A364" s="22" t="s">
         <v>1591</v>
       </c>
@@ -28297,7 +28297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="210">
       <c r="A365" s="22" t="s">
         <v>1593</v>
       </c>
@@ -28353,7 +28353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="210">
       <c r="A366" s="22" t="s">
         <v>1596</v>
       </c>
@@ -28409,7 +28409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="60">
       <c r="A367" s="22" t="s">
         <v>1599</v>
       </c>
@@ -28465,7 +28465,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="60">
       <c r="A368" s="22" t="s">
         <v>1602</v>
       </c>
@@ -28521,7 +28521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="60" hidden="1">
       <c r="A369" s="22" t="s">
         <v>1605</v>
       </c>
@@ -28577,7 +28577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="60" hidden="1">
       <c r="A370" s="22" t="s">
         <v>1607</v>
       </c>
@@ -28633,7 +28633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="60" hidden="1">
       <c r="A371" s="22" t="s">
         <v>1609</v>
       </c>
@@ -28689,7 +28689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="60" hidden="1">
       <c r="A372" s="22" t="s">
         <v>1611</v>
       </c>
@@ -28745,7 +28745,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ht="60" hidden="1">
       <c r="A373" s="22" t="s">
         <v>1613</v>
       </c>
@@ -28801,7 +28801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ht="60" hidden="1">
       <c r="A374" s="22" t="s">
         <v>1614</v>
       </c>
@@ -28857,7 +28857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" ht="60">
       <c r="A375" s="22" t="s">
         <v>1617</v>
       </c>
@@ -28913,7 +28913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" ht="60">
       <c r="A376" s="22" t="s">
         <v>1620</v>
       </c>
@@ -28969,7 +28969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" ht="60">
       <c r="A377" s="22" t="s">
         <v>1623</v>
       </c>
@@ -29025,7 +29025,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ht="60" hidden="1">
       <c r="A378" s="22" t="s">
         <v>1626</v>
       </c>
@@ -29081,7 +29081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ht="75" hidden="1">
       <c r="A379" s="22" t="s">
         <v>1629</v>
       </c>
@@ -29137,7 +29137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ht="60" hidden="1">
       <c r="A380" s="22" t="s">
         <v>1632</v>
       </c>
@@ -29193,7 +29193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ht="90" hidden="1">
       <c r="A381" s="22" t="s">
         <v>1635</v>
       </c>
@@ -29249,7 +29249,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" ht="75">
       <c r="A382" s="22" t="s">
         <v>1638</v>
       </c>
@@ -29305,7 +29305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" ht="75">
       <c r="A383" s="22" t="s">
         <v>1641</v>
       </c>
@@ -29361,7 +29361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" ht="60">
       <c r="A384" s="22" t="s">
         <v>1644</v>
       </c>
@@ -29417,7 +29417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" ht="60">
       <c r="A385" s="22" t="s">
         <v>1647</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="386" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:18" ht="60">
       <c r="A386" s="22" t="s">
         <v>1650</v>
       </c>
@@ -29529,7 +29529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" ht="60">
       <c r="A387" s="22" t="s">
         <v>1653</v>
       </c>
@@ -29585,12 +29585,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" ht="60" hidden="1">
       <c r="A388" s="22" t="s">
         <v>1656</v>
       </c>
       <c r="B388" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C388" s="18" t="s">
         <v>1658</v>
@@ -29641,7 +29641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ht="60" hidden="1">
       <c r="A389" s="22" t="s">
         <v>1660</v>
       </c>
@@ -29697,7 +29697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ht="60" hidden="1">
       <c r="A390" s="22" t="s">
         <v>1663</v>
       </c>
@@ -29753,7 +29753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ht="60" hidden="1">
       <c r="A391" s="22" t="s">
         <v>1666</v>
       </c>
@@ -29809,7 +29809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ht="60" hidden="1">
       <c r="A392" s="22" t="s">
         <v>1669</v>
       </c>
@@ -29865,7 +29865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ht="60" hidden="1">
       <c r="A393" s="22" t="s">
         <v>1672</v>
       </c>
@@ -29921,12 +29921,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" ht="60" hidden="1">
       <c r="A394" s="22" t="s">
         <v>1675</v>
       </c>
       <c r="B394" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C394" s="18" t="s">
         <v>1676</v>
@@ -29977,12 +29977,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" ht="60" hidden="1">
       <c r="A395" s="22" t="s">
         <v>1678</v>
       </c>
       <c r="B395" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C395" s="18" t="s">
         <v>1679</v>
@@ -30033,12 +30033,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" ht="60" hidden="1">
       <c r="A396" s="22" t="s">
         <v>1681</v>
       </c>
       <c r="B396" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C396" s="18" t="s">
         <v>1682</v>
@@ -30089,7 +30089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" ht="75" hidden="1">
       <c r="A397" s="22" t="s">
         <v>1684</v>
       </c>
@@ -30145,12 +30145,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" ht="60" hidden="1">
       <c r="A398" s="22" t="s">
         <v>1687</v>
       </c>
       <c r="B398" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C398" s="18" t="s">
         <v>1688</v>
@@ -30201,12 +30201,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" ht="60" hidden="1">
       <c r="A399" s="22" t="s">
         <v>1689</v>
       </c>
       <c r="B399" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C399" s="18" t="s">
         <v>1690</v>
@@ -30257,12 +30257,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" ht="60" hidden="1">
       <c r="A400" s="22" t="s">
         <v>1691</v>
       </c>
       <c r="B400" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C400" s="18" t="s">
         <v>1692</v>
@@ -30313,12 +30313,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" ht="75" hidden="1">
       <c r="A401" s="22" t="s">
         <v>1694</v>
       </c>
       <c r="B401" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C401" s="18" t="s">
         <v>1695</v>
@@ -30369,12 +30369,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="402" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" ht="75" hidden="1">
       <c r="A402" s="22" t="s">
         <v>1697</v>
       </c>
       <c r="B402" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C402" s="18" t="s">
         <v>1698</v>
@@ -30425,7 +30425,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" ht="60" hidden="1">
       <c r="A403" s="22" t="s">
         <v>1700</v>
       </c>
@@ -30481,12 +30481,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" ht="60" hidden="1">
       <c r="A404" s="22" t="s">
         <v>1703</v>
       </c>
       <c r="B404" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C404" s="18" t="s">
         <v>1704</v>
@@ -30537,12 +30537,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" ht="60" hidden="1">
       <c r="A405" s="22" t="s">
         <v>1706</v>
       </c>
       <c r="B405" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C405" s="18" t="s">
         <v>1707</v>
@@ -30593,12 +30593,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" ht="60" hidden="1">
       <c r="A406" s="22" t="s">
         <v>1709</v>
       </c>
       <c r="B406" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C406" s="18" t="s">
         <v>1710</v>
@@ -30649,12 +30649,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" ht="60" hidden="1">
       <c r="A407" s="22" t="s">
         <v>1712</v>
       </c>
       <c r="B407" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C407" s="18" t="s">
         <v>1713</v>
@@ -30705,12 +30705,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" ht="60" hidden="1">
       <c r="A408" s="22" t="s">
         <v>1715</v>
       </c>
       <c r="B408" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C408" s="18" t="s">
         <v>1716</v>
@@ -30761,12 +30761,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" ht="60" hidden="1">
       <c r="A409" s="22" t="s">
         <v>1718</v>
       </c>
       <c r="B409" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C409" s="18" t="s">
         <v>1719</v>
@@ -30817,12 +30817,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" ht="195" hidden="1">
       <c r="A410" s="22" t="s">
         <v>1721</v>
       </c>
       <c r="B410" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C410" s="18" t="s">
         <v>1722</v>
@@ -30873,12 +30873,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" ht="60" hidden="1">
       <c r="A411" s="22" t="s">
         <v>1724</v>
       </c>
       <c r="B411" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C411" s="18" t="s">
         <v>1725</v>
@@ -30929,12 +30929,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" ht="60" hidden="1">
       <c r="A412" s="22" t="s">
         <v>1727</v>
       </c>
       <c r="B412" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C412" s="18" t="s">
         <v>1728</v>
@@ -30985,12 +30985,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" ht="60" hidden="1">
       <c r="A413" s="22" t="s">
         <v>1730</v>
       </c>
       <c r="B413" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C413" s="18" t="s">
         <v>1732</v>
@@ -31041,7 +31041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" ht="60">
       <c r="A414" s="22" t="s">
         <v>1734</v>
       </c>
@@ -31097,7 +31097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" ht="60">
       <c r="A415" s="22" t="s">
         <v>1736</v>
       </c>
@@ -31153,7 +31153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" ht="60">
       <c r="A416" s="22" t="s">
         <v>1738</v>
       </c>
@@ -31209,7 +31209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" ht="60">
       <c r="A417" s="22" t="s">
         <v>1741</v>
       </c>
@@ -31265,7 +31265,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" ht="60">
       <c r="A418" s="22" t="s">
         <v>1744</v>
       </c>
@@ -31321,7 +31321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" ht="60">
       <c r="A419" s="22" t="s">
         <v>1747</v>
       </c>
@@ -31377,7 +31377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" ht="60">
       <c r="A420" s="22" t="s">
         <v>1750</v>
       </c>
@@ -31433,7 +31433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" ht="75">
       <c r="A421" s="22" t="s">
         <v>1752</v>
       </c>
@@ -31489,7 +31489,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" ht="75">
       <c r="A422" s="22" t="s">
         <v>1755</v>
       </c>
@@ -31545,7 +31545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" ht="75" hidden="1">
       <c r="A423" s="22" t="s">
         <v>1758</v>
       </c>
@@ -31601,7 +31601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" ht="75" hidden="1">
       <c r="A424" s="22" t="s">
         <v>1761</v>
       </c>
@@ -31657,7 +31657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" ht="409.5">
       <c r="A425" s="22" t="s">
         <v>1764</v>
       </c>
@@ -31713,7 +31713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" ht="60">
       <c r="A426" s="22" t="s">
         <v>1767</v>
       </c>
@@ -31769,7 +31769,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" ht="60" hidden="1">
       <c r="A427" s="22" t="s">
         <v>1771</v>
       </c>
@@ -31825,7 +31825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" ht="60" hidden="1">
       <c r="A428" s="22" t="s">
         <v>1774</v>
       </c>
@@ -31881,7 +31881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" ht="60">
       <c r="A429" s="22" t="s">
         <v>1777</v>
       </c>
@@ -31937,7 +31937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="75">
       <c r="A430" s="22" t="s">
         <v>1780</v>
       </c>
@@ -31993,7 +31993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="75" hidden="1">
       <c r="A431" s="22" t="s">
         <v>1783</v>
       </c>
@@ -32049,7 +32049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="60" hidden="1">
       <c r="A432" s="22" t="s">
         <v>1786</v>
       </c>
@@ -32105,7 +32105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="60">
       <c r="A433" s="22" t="s">
         <v>1789</v>
       </c>
@@ -32161,7 +32161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="60">
       <c r="A434" s="22" t="s">
         <v>1792</v>
       </c>
@@ -32217,7 +32217,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="330" hidden="1">
       <c r="A435" s="22" t="s">
         <v>189</v>
       </c>
@@ -32273,7 +32273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="330" hidden="1">
       <c r="A436" s="22" t="s">
         <v>195</v>
       </c>
@@ -32329,7 +32329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" ht="105" hidden="1">
       <c r="A437" s="22" t="s">
         <v>310</v>
       </c>
@@ -32385,7 +32385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="105" hidden="1">
       <c r="A438" s="22" t="s">
         <v>313</v>
       </c>
@@ -32441,7 +32441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="105" hidden="1">
       <c r="A439" s="22" t="s">
         <v>315</v>
       </c>
@@ -32497,7 +32497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="105" hidden="1">
       <c r="A440" s="22" t="s">
         <v>318</v>
       </c>
@@ -32553,7 +32553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="60" hidden="1">
       <c r="A441" s="22" t="s">
         <v>353</v>
       </c>
@@ -32609,7 +32609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="60" hidden="1">
       <c r="A442" s="22" t="s">
         <v>356</v>
       </c>
@@ -32665,7 +32665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="60" hidden="1">
       <c r="A443" s="22" t="s">
         <v>361</v>
       </c>
@@ -32721,7 +32721,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="90" hidden="1">
       <c r="A444" s="22" t="s">
         <v>433</v>
       </c>
@@ -32777,7 +32777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="90" hidden="1">
       <c r="A445" s="22" t="s">
         <v>436</v>
       </c>
@@ -32833,7 +32833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="75" hidden="1">
       <c r="A446" s="22" t="s">
         <v>506</v>
       </c>
@@ -32889,7 +32889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="75" hidden="1">
       <c r="A447" s="22" t="s">
         <v>509</v>
       </c>
@@ -32945,7 +32945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="60" hidden="1">
       <c r="A448" s="23" t="s">
         <v>512</v>
       </c>
@@ -33001,7 +33001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="60" hidden="1">
       <c r="A449" s="22" t="s">
         <v>549</v>
       </c>
@@ -33057,7 +33057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="60" hidden="1">
       <c r="A450" s="22" t="s">
         <v>551</v>
       </c>
@@ -33113,7 +33113,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="60" hidden="1">
       <c r="A451" s="22" t="s">
         <v>553</v>
       </c>
@@ -33169,7 +33169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="60" hidden="1">
       <c r="A452" s="22" t="s">
         <v>555</v>
       </c>
@@ -33225,7 +33225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="60" hidden="1">
       <c r="A453" s="22" t="s">
         <v>557</v>
       </c>
@@ -33281,7 +33281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="60" hidden="1">
       <c r="A454" s="22" t="s">
         <v>559</v>
       </c>
@@ -33337,7 +33337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="60" hidden="1">
       <c r="A455" s="22" t="s">
         <v>561</v>
       </c>
@@ -33393,7 +33393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="60" hidden="1">
       <c r="A456" s="22" t="s">
         <v>568</v>
       </c>
@@ -33449,7 +33449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="60" hidden="1">
       <c r="A457" s="22" t="s">
         <v>571</v>
       </c>
@@ -33505,7 +33505,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="345" hidden="1">
       <c r="A458" s="22" t="s">
         <v>679</v>
       </c>
@@ -33561,7 +33561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="345" hidden="1">
       <c r="A459" s="22" t="s">
         <v>682</v>
       </c>
@@ -33617,7 +33617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" ht="150" hidden="1">
       <c r="A460" s="22" t="s">
         <v>746</v>
       </c>
@@ -33673,7 +33673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="60" hidden="1">
       <c r="A461" s="22" t="s">
         <v>346</v>
       </c>
@@ -33729,7 +33729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="60" hidden="1">
       <c r="A462" s="22" t="s">
         <v>350</v>
       </c>
@@ -33785,7 +33785,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="60" hidden="1">
       <c r="A463" s="22" t="s">
         <v>359</v>
       </c>
@@ -33841,7 +33841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="345" hidden="1">
       <c r="A464" s="22" t="s">
         <v>677</v>
       </c>
@@ -33897,7 +33897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="409.5" hidden="1">
       <c r="A465" s="22" t="s">
         <v>861</v>
       </c>
@@ -33953,7 +33953,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="409.5" hidden="1">
       <c r="A466" s="22" t="s">
         <v>863</v>
       </c>
@@ -34009,7 +34009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="409.5" hidden="1">
       <c r="A467" s="22" t="s">
         <v>875</v>
       </c>
@@ -34065,7 +34065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="60" hidden="1">
       <c r="A468" s="22" t="s">
         <v>886</v>
       </c>
@@ -34121,7 +34121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:18" ht="60" hidden="1">
       <c r="A469" s="22" t="s">
         <v>887</v>
       </c>
@@ -34177,7 +34177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:18" ht="60" hidden="1">
       <c r="A470" s="22" t="s">
         <v>890</v>
       </c>
@@ -34233,7 +34233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:18" ht="60" hidden="1">
       <c r="A471" s="22" t="s">
         <v>898</v>
       </c>
@@ -34289,7 +34289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="345" hidden="1">
       <c r="A472" s="22" t="s">
         <v>731</v>
       </c>
@@ -34345,7 +34345,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="150" hidden="1">
       <c r="A473" s="22" t="s">
         <v>740</v>
       </c>
@@ -34401,7 +34401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="150" hidden="1">
       <c r="A474" s="22" t="s">
         <v>742</v>
       </c>
@@ -34457,7 +34457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="60" hidden="1">
       <c r="A475" s="22" t="s">
         <v>781</v>
       </c>
@@ -34513,7 +34513,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="60" hidden="1">
       <c r="A476" s="22" t="s">
         <v>783</v>
       </c>
@@ -34569,7 +34569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="60" hidden="1">
       <c r="A477" s="22" t="s">
         <v>784</v>
       </c>
@@ -34625,7 +34625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="409.5" hidden="1">
       <c r="A478" s="22" t="s">
         <v>821</v>
       </c>
@@ -34681,7 +34681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="409.5" hidden="1">
       <c r="A479" s="22" t="s">
         <v>823</v>
       </c>
@@ -34737,7 +34737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="409.5" hidden="1">
       <c r="A480" s="22" t="s">
         <v>825</v>
       </c>
@@ -34793,7 +34793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="409.5" hidden="1">
       <c r="A481" s="22" t="s">
         <v>827</v>
       </c>
@@ -34849,7 +34849,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="409.5" hidden="1">
       <c r="A482" s="22" t="s">
         <v>829</v>
       </c>
@@ -34905,7 +34905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="409.5" hidden="1">
       <c r="A483" s="22" t="s">
         <v>836</v>
       </c>
@@ -34961,7 +34961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="409.5" hidden="1">
       <c r="A484" s="22" t="s">
         <v>839</v>
       </c>
@@ -35017,7 +35017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="409.5" hidden="1">
       <c r="A485" s="22" t="s">
         <v>842</v>
       </c>
@@ -35073,7 +35073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="409.5" hidden="1">
       <c r="A486" s="22" t="s">
         <v>845</v>
       </c>
@@ -35129,7 +35129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="409.5" hidden="1">
       <c r="A487" s="22" t="s">
         <v>848</v>
       </c>
@@ -35185,7 +35185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="60" hidden="1">
       <c r="A488" s="22" t="s">
         <v>524</v>
       </c>
@@ -35241,7 +35241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="60" hidden="1">
       <c r="A489" s="22" t="s">
         <v>527</v>
       </c>
@@ -35297,7 +35297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="60" hidden="1">
       <c r="A490" s="22" t="s">
         <v>529</v>
       </c>
@@ -35353,7 +35353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="60" hidden="1">
       <c r="A491" s="22" t="s">
         <v>532</v>
       </c>
@@ -35409,7 +35409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="60" hidden="1">
       <c r="A492" s="22" t="s">
         <v>535</v>
       </c>
@@ -35465,7 +35465,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="60" hidden="1">
       <c r="A493" s="22" t="s">
         <v>538</v>
       </c>
@@ -35521,7 +35521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="60" hidden="1">
       <c r="A494" s="22" t="s">
         <v>541</v>
       </c>
@@ -35577,7 +35577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="60" hidden="1">
       <c r="A495" s="22" t="s">
         <v>544</v>
       </c>
@@ -35633,7 +35633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="60" hidden="1">
       <c r="A496" s="22" t="s">
         <v>547</v>
       </c>
@@ -35689,7 +35689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="345" hidden="1">
       <c r="A497" s="22" t="s">
         <v>620</v>
       </c>
@@ -35745,7 +35745,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="345" hidden="1">
       <c r="A498" s="22" t="s">
         <v>622</v>
       </c>
@@ -35801,7 +35801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="345" hidden="1">
       <c r="A499" s="22" t="s">
         <v>625</v>
       </c>
@@ -35857,7 +35857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="345" hidden="1">
       <c r="A500" s="22" t="s">
         <v>626</v>
       </c>
@@ -35913,7 +35913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="345" hidden="1">
       <c r="A501" s="22" t="s">
         <v>629</v>
       </c>
@@ -35969,7 +35969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" ht="345" hidden="1">
       <c r="A502" s="22" t="s">
         <v>632</v>
       </c>
@@ -36025,7 +36025,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="345" hidden="1">
       <c r="A503" s="22" t="s">
         <v>636</v>
       </c>
@@ -36081,7 +36081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="345" hidden="1">
       <c r="A504" s="22" t="s">
         <v>666</v>
       </c>
@@ -36137,7 +36137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="345" hidden="1">
       <c r="A505" s="22" t="s">
         <v>669</v>
       </c>
@@ -36193,7 +36193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:18" ht="345" hidden="1">
       <c r="A506" s="22" t="s">
         <v>672</v>
       </c>
@@ -36249,7 +36249,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="345" hidden="1">
       <c r="A507" s="22" t="s">
         <v>674</v>
       </c>
@@ -36305,7 +36305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="345" hidden="1">
       <c r="A508" s="22" t="s">
         <v>676</v>
       </c>
@@ -36361,7 +36361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="60" hidden="1">
       <c r="A509" s="22" t="s">
         <v>488</v>
       </c>
@@ -36417,7 +36417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="60" hidden="1">
       <c r="A510" s="22" t="s">
         <v>491</v>
       </c>
@@ -36473,7 +36473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:18" ht="60" hidden="1">
       <c r="A511" s="22" t="s">
         <v>497</v>
       </c>
@@ -36529,7 +36529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:18" ht="60" hidden="1">
       <c r="A512" s="22" t="s">
         <v>516</v>
       </c>
@@ -36585,7 +36585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" ht="60" hidden="1">
       <c r="A513" s="22" t="s">
         <v>519</v>
       </c>
@@ -36641,7 +36641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="60" hidden="1">
       <c r="A514" s="22" t="s">
         <v>521</v>
       </c>
@@ -36697,7 +36697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="60" hidden="1">
       <c r="A515" s="22" t="s">
         <v>372</v>
       </c>
@@ -36753,7 +36753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="60" hidden="1">
       <c r="A516" s="22" t="s">
         <v>388</v>
       </c>
@@ -36809,7 +36809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="60" hidden="1">
       <c r="A517" s="22" t="s">
         <v>469</v>
       </c>
@@ -36865,7 +36865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="60" hidden="1">
       <c r="A518" s="22" t="s">
         <v>472</v>
       </c>
@@ -36921,7 +36921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="60" hidden="1">
       <c r="A519" s="22" t="s">
         <v>474</v>
       </c>
@@ -36977,7 +36977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="60" hidden="1">
       <c r="A520" s="22" t="s">
         <v>476</v>
       </c>
@@ -37033,7 +37033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="60" hidden="1">
       <c r="A521" s="22" t="s">
         <v>479</v>
       </c>
@@ -37089,7 +37089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="60" hidden="1">
       <c r="A522" s="22" t="s">
         <v>482</v>
       </c>
@@ -37145,7 +37145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="60" hidden="1">
       <c r="A523" s="22" t="s">
         <v>485</v>
       </c>
@@ -37201,7 +37201,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="345" hidden="1">
       <c r="A524" s="22" t="s">
         <v>635</v>
       </c>
@@ -37257,7 +37257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="525" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="345" hidden="1">
       <c r="A525" s="22" t="s">
         <v>639</v>
       </c>
@@ -37313,7 +37313,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="345" hidden="1">
       <c r="A526" s="22" t="s">
         <v>642</v>
       </c>
@@ -37369,7 +37369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="345" hidden="1">
       <c r="A527" s="22" t="s">
         <v>643</v>
       </c>
@@ -37425,7 +37425,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="345" hidden="1">
       <c r="A528" s="22" t="s">
         <v>646</v>
       </c>
@@ -37481,7 +37481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="345" hidden="1">
       <c r="A529" s="22" t="s">
         <v>648</v>
       </c>
@@ -37537,7 +37537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="345" hidden="1">
       <c r="A530" s="22" t="s">
         <v>651</v>
       </c>
@@ -37593,7 +37593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="531" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="345" hidden="1">
       <c r="A531" s="22" t="s">
         <v>654</v>
       </c>
@@ -37649,7 +37649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="345" hidden="1">
       <c r="A532" s="22" t="s">
         <v>657</v>
       </c>
@@ -37705,7 +37705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="533" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="345" hidden="1">
       <c r="A533" s="22" t="s">
         <v>659</v>
       </c>
@@ -37761,7 +37761,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="345" hidden="1">
       <c r="A534" s="22" t="s">
         <v>661</v>
       </c>
@@ -37817,7 +37817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="345" hidden="1">
       <c r="A535" s="22" t="s">
         <v>663</v>
       </c>
@@ -37873,7 +37873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="135" hidden="1">
       <c r="A536" s="22" t="s">
         <v>694</v>
       </c>
@@ -37929,7 +37929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="537" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="135" hidden="1">
       <c r="A537" s="22" t="s">
         <v>697</v>
       </c>
@@ -37985,7 +37985,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="150" hidden="1">
       <c r="A538" s="22" t="s">
         <v>734</v>
       </c>
@@ -38041,7 +38041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="150" hidden="1">
       <c r="A539" s="22" t="s">
         <v>738</v>
       </c>
@@ -38097,7 +38097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="60" hidden="1">
       <c r="A540" s="22" t="s">
         <v>386</v>
       </c>
@@ -38153,7 +38153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="60" hidden="1">
       <c r="A541" s="22" t="s">
         <v>394</v>
       </c>
@@ -38209,7 +38209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="60" hidden="1">
       <c r="A542" s="22" t="s">
         <v>397</v>
       </c>
@@ -38265,7 +38265,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="60" hidden="1">
       <c r="A543" s="22" t="s">
         <v>399</v>
       </c>
@@ -38321,7 +38321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="544" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" ht="60" hidden="1">
       <c r="A544" s="22" t="s">
         <v>402</v>
       </c>
@@ -38377,7 +38377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="60" hidden="1">
       <c r="A545" s="22" t="s">
         <v>405</v>
       </c>
@@ -38433,7 +38433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="60" hidden="1">
       <c r="A546" s="22" t="s">
         <v>408</v>
       </c>
@@ -38489,7 +38489,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="75" hidden="1">
       <c r="A547" s="22" t="s">
         <v>411</v>
       </c>
@@ -38545,7 +38545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="90" hidden="1">
       <c r="A548" s="22" t="s">
         <v>423</v>
       </c>
@@ -38601,7 +38601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="549" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" ht="90" hidden="1">
       <c r="A549" s="22" t="s">
         <v>428</v>
       </c>
@@ -38657,7 +38657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" ht="60" hidden="1">
       <c r="A550" s="22" t="s">
         <v>451</v>
       </c>
@@ -38713,7 +38713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" ht="60" hidden="1">
       <c r="A551" s="22" t="s">
         <v>454</v>
       </c>
@@ -38769,7 +38769,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" ht="330" hidden="1">
       <c r="A552" s="22" t="s">
         <v>187</v>
       </c>
@@ -38825,7 +38825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="553" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:18" ht="60" hidden="1">
       <c r="A553" s="22" t="s">
         <v>331</v>
       </c>
@@ -38881,7 +38881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="554" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:18" ht="60" hidden="1">
       <c r="A554" s="22" t="s">
         <v>336</v>
       </c>
@@ -38937,7 +38937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="555" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:18" ht="60" hidden="1">
       <c r="A555" s="22" t="s">
         <v>364</v>
       </c>
@@ -38993,7 +38993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="556" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:18" ht="60" hidden="1">
       <c r="A556" s="22" t="s">
         <v>367</v>
       </c>
@@ -39049,7 +39049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="60" hidden="1">
       <c r="A557" s="22" t="s">
         <v>370</v>
       </c>
@@ -39105,7 +39105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="60" hidden="1">
       <c r="A558" s="22" t="s">
         <v>374</v>
       </c>
@@ -39161,7 +39161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="60" hidden="1">
       <c r="A559" s="22" t="s">
         <v>376</v>
       </c>
@@ -39217,7 +39217,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="60" hidden="1">
       <c r="A560" s="22" t="s">
         <v>379</v>
       </c>
@@ -39273,7 +39273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="60" hidden="1">
       <c r="A561" s="22" t="s">
         <v>382</v>
       </c>
@@ -39329,7 +39329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="60" hidden="1">
       <c r="A562" s="22" t="s">
         <v>384</v>
       </c>
@@ -39385,7 +39385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="60" hidden="1">
       <c r="A563" s="22" t="s">
         <v>391</v>
       </c>
@@ -39441,7 +39441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="60" hidden="1">
       <c r="A564" s="22" t="s">
         <v>325</v>
       </c>
@@ -39497,7 +39497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="60" hidden="1">
       <c r="A565" s="22" t="s">
         <v>329</v>
       </c>
@@ -39553,7 +39553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="60" hidden="1">
       <c r="A566" s="22" t="s">
         <v>321</v>
       </c>
@@ -39609,7 +39609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="567" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="60" hidden="1">
       <c r="A567" s="22" t="s">
         <v>327</v>
       </c>
@@ -39665,7 +39665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="60" hidden="1">
       <c r="A568" s="22" t="s">
         <v>333</v>
       </c>
@@ -39721,7 +39721,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="60" hidden="1">
       <c r="A569" s="22" t="s">
         <v>339</v>
       </c>
@@ -39777,7 +39777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="75" hidden="1">
       <c r="A570" s="22" t="s">
         <v>105</v>
       </c>
@@ -39833,7 +39833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="75" hidden="1">
       <c r="A571" s="22" t="s">
         <v>118</v>
       </c>
@@ -39889,7 +39889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="75" hidden="1">
       <c r="A572" s="22" t="s">
         <v>130</v>
       </c>
@@ -39945,7 +39945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="573" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="75" hidden="1">
       <c r="A573" s="22" t="s">
         <v>164</v>
       </c>
@@ -40001,7 +40001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="330" hidden="1">
       <c r="A574" s="22" t="s">
         <v>177</v>
       </c>
@@ -40057,7 +40057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="575" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="330" hidden="1">
       <c r="A575" s="22" t="s">
         <v>179</v>
       </c>
@@ -40113,7 +40113,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="330" hidden="1">
       <c r="A576" s="22" t="s">
         <v>197</v>
       </c>
@@ -40169,7 +40169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="330" hidden="1">
       <c r="A577" s="22" t="s">
         <v>199</v>
       </c>
@@ -40225,7 +40225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="75" hidden="1">
       <c r="A578" s="21" t="s">
         <v>18</v>
       </c>
@@ -40281,7 +40281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="75" hidden="1">
       <c r="A579" s="21" t="s">
         <v>33</v>
       </c>
@@ -40337,7 +40337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="105" hidden="1">
       <c r="A580" s="21" t="s">
         <v>35</v>
       </c>
@@ -40393,7 +40393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="75" hidden="1">
       <c r="A581" s="21" t="s">
         <v>43</v>
       </c>
@@ -40449,7 +40449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="75" hidden="1">
       <c r="A582" s="21" t="s">
         <v>47</v>
       </c>
@@ -40505,7 +40505,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="75" hidden="1">
       <c r="A583" s="21" t="s">
         <v>50</v>
       </c>
@@ -40561,7 +40561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="75" hidden="1">
       <c r="A584" s="22" t="s">
         <v>53</v>
       </c>
@@ -40617,7 +40617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="585" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="75" hidden="1">
       <c r="A585" s="22" t="s">
         <v>55</v>
       </c>
@@ -40673,7 +40673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="586" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" ht="75" hidden="1">
       <c r="A586" s="22" t="s">
         <v>57</v>
       </c>
@@ -40729,7 +40729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="587" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="75" hidden="1">
       <c r="A587" s="22" t="s">
         <v>59</v>
       </c>
@@ -40785,7 +40785,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="75" hidden="1">
       <c r="A588" s="22" t="s">
         <v>61</v>
       </c>
@@ -40841,7 +40841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="75" hidden="1">
       <c r="A589" s="22" t="s">
         <v>66</v>
       </c>
@@ -40897,7 +40897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="75" hidden="1">
       <c r="A590" s="22" t="s">
         <v>68</v>
       </c>
@@ -40953,7 +40953,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="591" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="195" hidden="1">
       <c r="A591" s="22" t="s">
         <v>71</v>
       </c>
@@ -41009,7 +41009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="195" hidden="1">
       <c r="A592" s="22" t="s">
         <v>75</v>
       </c>
@@ -41065,7 +41065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="195" hidden="1">
       <c r="A593" s="22" t="s">
         <v>77</v>
       </c>
@@ -41121,7 +41121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="195" hidden="1">
       <c r="A594" s="22" t="s">
         <v>80</v>
       </c>
@@ -41177,7 +41177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="595" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:18" ht="195" hidden="1">
       <c r="A595" s="22" t="s">
         <v>84</v>
       </c>
@@ -41233,7 +41233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="596" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:18" ht="195" hidden="1">
       <c r="A596" s="22" t="s">
         <v>87</v>
       </c>
@@ -41289,7 +41289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="597" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:18" ht="195" hidden="1">
       <c r="A597" s="22" t="s">
         <v>89</v>
       </c>
@@ -41345,7 +41345,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="598" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="195" hidden="1">
       <c r="A598" s="22" t="s">
         <v>91</v>
       </c>
@@ -41401,7 +41401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="195" hidden="1">
       <c r="A599" s="22" t="s">
         <v>93</v>
       </c>
@@ -41457,7 +41457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="195" hidden="1">
       <c r="A600" s="22" t="s">
         <v>95</v>
       </c>
@@ -41513,7 +41513,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="195" hidden="1">
       <c r="A601" s="22" t="s">
         <v>97</v>
       </c>
@@ -41569,7 +41569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="75" hidden="1">
       <c r="A602" s="22" t="s">
         <v>108</v>
       </c>
@@ -41625,7 +41625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="75" hidden="1">
       <c r="A603" s="22" t="s">
         <v>110</v>
       </c>
@@ -41681,7 +41681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="75" hidden="1">
       <c r="A604" s="22" t="s">
         <v>112</v>
       </c>
@@ -41737,7 +41737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="75" hidden="1">
       <c r="A605" s="22" t="s">
         <v>114</v>
       </c>
@@ -41793,7 +41793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="606" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:18" ht="75" hidden="1">
       <c r="A606" s="22" t="s">
         <v>116</v>
       </c>
@@ -41849,7 +41849,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="75" hidden="1">
       <c r="A607" s="22" t="s">
         <v>120</v>
       </c>
@@ -41905,7 +41905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="75" hidden="1">
       <c r="A608" s="22" t="s">
         <v>125</v>
       </c>
@@ -41961,7 +41961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" ht="75" hidden="1">
       <c r="A609" s="22" t="s">
         <v>127</v>
       </c>
@@ -42017,7 +42017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:18" ht="75" hidden="1">
       <c r="A610" s="22" t="s">
         <v>136</v>
       </c>
@@ -42073,7 +42073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" ht="75" hidden="1">
       <c r="A611" s="22" t="s">
         <v>138</v>
       </c>
@@ -42129,7 +42129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" ht="75" hidden="1">
       <c r="A612" s="22" t="s">
         <v>140</v>
       </c>
@@ -42185,7 +42185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" ht="75" hidden="1">
       <c r="A613" s="22" t="s">
         <v>142</v>
       </c>
@@ -42241,7 +42241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" ht="75" hidden="1">
       <c r="A614" s="22" t="s">
         <v>144</v>
       </c>
@@ -42297,7 +42297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" ht="75" hidden="1">
       <c r="A615" s="22" t="s">
         <v>146</v>
       </c>
@@ -42353,7 +42353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" ht="75" hidden="1">
       <c r="A616" s="22" t="s">
         <v>148</v>
       </c>
@@ -42409,7 +42409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" ht="345" hidden="1">
       <c r="A617" s="22" t="s">
         <v>152</v>
       </c>
@@ -42465,7 +42465,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" ht="135" hidden="1">
       <c r="A618" s="22" t="s">
         <v>156</v>
       </c>
@@ -42521,7 +42521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:18" ht="409.5" hidden="1">
       <c r="A619" s="22" t="s">
         <v>160</v>
       </c>
@@ -42577,7 +42577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" ht="75" hidden="1">
       <c r="A620" s="22" t="s">
         <v>167</v>
       </c>
@@ -42633,7 +42633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" ht="75" hidden="1">
       <c r="A621" s="22" t="s">
         <v>169</v>
       </c>
@@ -42689,7 +42689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" ht="75" hidden="1">
       <c r="A622" s="22" t="s">
         <v>172</v>
       </c>
@@ -42745,7 +42745,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" ht="330" hidden="1">
       <c r="A623" s="22" t="s">
         <v>174</v>
       </c>
@@ -42801,7 +42801,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" ht="330" hidden="1">
       <c r="A624" s="22" t="s">
         <v>181</v>
       </c>
@@ -42857,7 +42857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="330" hidden="1">
       <c r="A625" s="22" t="s">
         <v>183</v>
       </c>
@@ -42913,7 +42913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="330" hidden="1">
       <c r="A626" s="22" t="s">
         <v>185</v>
       </c>
@@ -42969,7 +42969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="330" hidden="1">
       <c r="A627" s="22" t="s">
         <v>191</v>
       </c>
@@ -43025,7 +43025,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:18" ht="330" hidden="1">
       <c r="A628" s="22" t="s">
         <v>193</v>
       </c>
@@ -43081,7 +43081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="629" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:18" ht="330" hidden="1">
       <c r="A629" s="22" t="s">
         <v>200</v>
       </c>
@@ -43137,7 +43137,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:18" ht="330" hidden="1">
       <c r="A630" s="22" t="s">
         <v>202</v>
       </c>
@@ -43193,7 +43193,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:18" ht="330" hidden="1">
       <c r="A631" s="22" t="s">
         <v>204</v>
       </c>
@@ -43249,7 +43249,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:18" ht="330" hidden="1">
       <c r="A632" s="22" t="s">
         <v>206</v>
       </c>
@@ -43305,7 +43305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="633" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:18" ht="60" hidden="1">
       <c r="A633" s="22" t="s">
         <v>208</v>
       </c>
@@ -43361,7 +43361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:18" ht="60" hidden="1">
       <c r="A634" s="22" t="s">
         <v>215</v>
       </c>
@@ -43417,7 +43417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:18" ht="60" hidden="1">
       <c r="A635" s="22" t="s">
         <v>216</v>
       </c>
@@ -43473,7 +43473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:18" ht="60" hidden="1">
       <c r="A636" s="22" t="s">
         <v>217</v>
       </c>
@@ -43529,7 +43529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="637" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:18" ht="60" hidden="1">
       <c r="A637" s="22" t="s">
         <v>232</v>
       </c>
@@ -43585,7 +43585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="638" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:18" ht="60" hidden="1">
       <c r="A638" s="22" t="s">
         <v>234</v>
       </c>
@@ -43641,7 +43641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="639" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:18" ht="60" hidden="1">
       <c r="A639" s="22" t="s">
         <v>237</v>
       </c>
@@ -43697,7 +43697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="640" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:18" ht="60" hidden="1">
       <c r="A640" s="22" t="s">
         <v>242</v>
       </c>
@@ -43753,7 +43753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="641" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:18" ht="60" hidden="1">
       <c r="A641" s="22" t="s">
         <v>245</v>
       </c>
@@ -43809,7 +43809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="642" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:18" ht="60" hidden="1">
       <c r="A642" s="22" t="s">
         <v>248</v>
       </c>
@@ -43865,7 +43865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="643" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:18" ht="60" hidden="1">
       <c r="A643" s="22" t="s">
         <v>250</v>
       </c>
@@ -43921,7 +43921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="644" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:18" ht="60" hidden="1">
       <c r="A644" s="22" t="s">
         <v>253</v>
       </c>
@@ -43977,7 +43977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="645" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:18" ht="60" hidden="1">
       <c r="A645" s="22" t="s">
         <v>254</v>
       </c>
@@ -44033,7 +44033,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="646" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:18" ht="60" hidden="1">
       <c r="A646" s="22" t="s">
         <v>256</v>
       </c>
@@ -44089,7 +44089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="647" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:18" ht="60" hidden="1">
       <c r="A647" s="22" t="s">
         <v>258</v>
       </c>
@@ -44145,7 +44145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="648" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:18" ht="60" hidden="1">
       <c r="A648" s="22" t="s">
         <v>260</v>
       </c>
@@ -44201,7 +44201,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="649" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:18" ht="60" hidden="1">
       <c r="A649" s="22" t="s">
         <v>264</v>
       </c>
@@ -44257,7 +44257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="650" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:18" ht="60" hidden="1">
       <c r="A650" s="22" t="s">
         <v>267</v>
       </c>
@@ -44313,7 +44313,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="651" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:18" ht="75" hidden="1">
       <c r="A651" s="22" t="s">
         <v>268</v>
       </c>
@@ -44369,7 +44369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="652" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:18" ht="60" hidden="1">
       <c r="A652" s="22" t="s">
         <v>271</v>
       </c>
@@ -44425,7 +44425,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="653" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:18" ht="60" hidden="1">
       <c r="A653" s="22" t="s">
         <v>273</v>
       </c>
@@ -44481,7 +44481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="654" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:18" ht="60" hidden="1">
       <c r="A654" s="22" t="s">
         <v>276</v>
       </c>
@@ -44537,7 +44537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="655" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:18" ht="60" hidden="1">
       <c r="A655" s="22" t="s">
         <v>279</v>
       </c>
@@ -44593,7 +44593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="656" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:18" ht="60" hidden="1">
       <c r="A656" s="22" t="s">
         <v>282</v>
       </c>
@@ -44649,7 +44649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="657" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:18" ht="60" hidden="1">
       <c r="A657" s="22" t="s">
         <v>285</v>
       </c>
@@ -44705,7 +44705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="658" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:18" ht="60" hidden="1">
       <c r="A658" s="22" t="s">
         <v>287</v>
       </c>
@@ -44761,7 +44761,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="659" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:18" ht="60" hidden="1">
       <c r="A659" s="22" t="s">
         <v>289</v>
       </c>
@@ -44817,7 +44817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="660" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:18" ht="60" hidden="1">
       <c r="A660" s="22" t="s">
         <v>292</v>
       </c>
@@ -44873,7 +44873,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="661" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:18" ht="105" hidden="1">
       <c r="A661" s="22" t="s">
         <v>294</v>
       </c>
@@ -44929,7 +44929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="662" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:18" ht="105" hidden="1">
       <c r="A662" s="22" t="s">
         <v>296</v>
       </c>
@@ -44985,7 +44985,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="663" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:18" ht="105" hidden="1">
       <c r="A663" s="22" t="s">
         <v>299</v>
       </c>
@@ -45041,7 +45041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="664" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:18" ht="105" hidden="1">
       <c r="A664" s="22" t="s">
         <v>302</v>
       </c>
@@ -45097,7 +45097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="665" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:18" ht="105" hidden="1">
       <c r="A665" s="22" t="s">
         <v>305</v>
       </c>
@@ -45153,7 +45153,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="666" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:18" ht="105" hidden="1">
       <c r="A666" s="22" t="s">
         <v>308</v>
       </c>
@@ -45246,7 +45246,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -45256,7 +45256,7 @@
     <col min="6" max="6" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="105.75" customHeight="1">
       <c r="B3" s="27" t="s">
         <v>1796</v>
       </c>
@@ -45266,7 +45266,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>1935</v>
       </c>
@@ -45287,7 +45287,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="22.5">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -45308,7 +45308,7 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="22.5">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -45329,7 +45329,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -45350,7 +45350,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -45371,7 +45371,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="22.5">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -45392,7 +45392,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -45413,7 +45413,7 @@
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="22.5">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -45434,7 +45434,7 @@
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -45455,7 +45455,7 @@
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="7">
         <v>9</v>
       </c>
@@ -45476,7 +45476,7 @@
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="22.5">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -45497,7 +45497,7 @@
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="22.5">
       <c r="A15" s="7">
         <v>11</v>
       </c>
@@ -45518,7 +45518,7 @@
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -45539,7 +45539,7 @@
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="22.5">
       <c r="A17" s="7">
         <v>13</v>
       </c>
@@ -45560,7 +45560,7 @@
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="22.5">
       <c r="A18" s="7">
         <v>14</v>
       </c>
@@ -45581,7 +45581,7 @@
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="7">
         <v>15</v>
       </c>
@@ -45602,7 +45602,7 @@
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="7">
         <v>16</v>
       </c>
@@ -45623,7 +45623,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="22.5">
       <c r="A21" s="7">
         <v>17</v>
       </c>
@@ -45644,7 +45644,7 @@
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="7">
         <v>18</v>
       </c>
@@ -45665,7 +45665,7 @@
       </c>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="22.5">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -45686,7 +45686,7 @@
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="22.5">
       <c r="A24" s="7">
         <v>20</v>
       </c>
@@ -45707,7 +45707,7 @@
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="7">
         <v>21</v>
       </c>
@@ -45728,7 +45728,7 @@
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="22.5">
       <c r="A26" s="7">
         <v>22</v>
       </c>
@@ -45749,7 +45749,7 @@
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="22.5">
       <c r="A27" s="7">
         <v>23</v>
       </c>
@@ -45770,7 +45770,7 @@
       </c>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="7">
         <v>24</v>
       </c>
@@ -45791,7 +45791,7 @@
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="7">
         <v>25</v>
       </c>
@@ -45812,7 +45812,7 @@
       </c>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="22.5">
       <c r="A30" s="7">
         <v>26</v>
       </c>
@@ -45833,7 +45833,7 @@
       </c>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="22.5">
       <c r="A31" s="7">
         <v>27</v>
       </c>
@@ -45854,7 +45854,7 @@
       </c>
       <c r="G31" s="7"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5">
       <c r="B36" s="10" t="s">
         <v>1936</v>
       </c>
@@ -45868,7 +45868,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5">
       <c r="B37" s="5" t="s">
         <v>1937</v>
       </c>
@@ -45882,7 +45882,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5">
       <c r="B38" s="5" t="s">
         <v>1940</v>
       </c>
@@ -45896,7 +45896,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" ht="30">
       <c r="B39" s="5" t="s">
         <v>1942</v>
       </c>
@@ -45910,7 +45910,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5">
       <c r="B40" s="5" t="s">
         <v>1493</v>
       </c>
@@ -45924,7 +45924,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5">
       <c r="B41" s="5" t="s">
         <v>808</v>
       </c>
@@ -45938,7 +45938,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5">
       <c r="B42" s="5" t="s">
         <v>1945</v>
       </c>
@@ -45952,7 +45952,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5">
       <c r="B43" s="5" t="s">
         <v>1946</v>
       </c>
@@ -45966,7 +45966,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5">
       <c r="B44" s="5" t="s">
         <v>662</v>
       </c>
@@ -45980,7 +45980,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5">
       <c r="B45" s="5" t="s">
         <v>1947</v>
       </c>
@@ -45994,7 +45994,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5">
       <c r="B46" s="5" t="s">
         <v>1948</v>
       </c>
@@ -46008,7 +46008,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5">
       <c r="B47" s="5" t="s">
         <v>1833</v>
       </c>
@@ -46034,13 +46034,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="103.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
         <v>1951</v>
       </c>
@@ -46048,7 +46048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>1955</v>
       </c>
@@ -46056,7 +46056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>1953</v>
       </c>
@@ -46064,7 +46064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>1952</v>
       </c>
@@ -46072,7 +46072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>1954</v>
       </c>
@@ -46080,7 +46080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>1956</v>
       </c>
@@ -46088,7 +46088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>1957</v>
       </c>
@@ -46096,7 +46096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="30">
       <c r="A8" s="4" t="s">
         <v>1958</v>
       </c>
@@ -46104,7 +46104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>1959</v>
       </c>
@@ -46112,7 +46112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="30">
       <c r="A10" t="s">
         <v>1960</v>
       </c>
@@ -46120,7 +46120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="30">
       <c r="A11" t="s">
         <v>1961</v>
       </c>
@@ -46128,7 +46128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="45">
       <c r="A12" t="s">
         <v>1962</v>
       </c>
@@ -46136,7 +46136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30">
       <c r="A13" t="s">
         <v>1963</v>
       </c>
@@ -46144,7 +46144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>1964</v>
       </c>
@@ -46152,7 +46152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="30">
       <c r="A15" t="s">
         <v>1965</v>
       </c>
@@ -46160,7 +46160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="30">
       <c r="A16" t="s">
         <v>1966</v>
       </c>
@@ -46168,37 +46168,37 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2">
       <c r="B17" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2">
       <c r="B21" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" s="2">
         <v>-1</v>
       </c>
